--- a/analytics/2026-new-patients-performance-to-budget.xlsx
+++ b/analytics/2026-new-patients-performance-to-budget.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Perf to Budget" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Trends" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Aug Scorecard" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Digital Context" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Paid Media" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Digital Context" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,11 +23,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);-"/>
     <numFmt numFmtId="167" formatCode="+0.0%;-0.0%;0.0%"/>
+    <numFmt numFmtId="168" formatCode="$#,##0"/>
+    <numFmt numFmtId="169" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -86,7 +89,7 @@
       <sz val="20"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +114,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -191,6 +199,17 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5276,8 +5295,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A4:J4"/>
   </mergeCells>
   <conditionalFormatting sqref="M19:M25">
@@ -6320,6 +6339,1507 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Paid Media — Google Ads, January through July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Source: Monthly_Data_on_Google_Ads_Performance_92.csv, keyword level, 1 Jan - 30 Jul 2026. Blue cells are inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Monthly totals — and the reconciliation against GA4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Total / avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>309482</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>290337</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>429891</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>339799</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>302709</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>341137</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>291599</v>
+      </c>
+      <c r="I6" s="9">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>16127</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>14464</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>21114</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>18136</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>15803</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>17493</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>16944</v>
+      </c>
+      <c r="I7" s="9">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n">
+        <v>169087.2</v>
+      </c>
+      <c r="C8" s="42" t="n">
+        <v>139994.19</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>283541.48</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>241541.3</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>212153.77</v>
+      </c>
+      <c r="G8" s="42" t="n">
+        <v>279448.97</v>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>262408.99</v>
+      </c>
+      <c r="I8" s="43">
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Reported conversions</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>1484.87</v>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>1128.45</v>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>1980.88</v>
+      </c>
+      <c r="E9" s="44" t="n">
+        <v>1682.11</v>
+      </c>
+      <c r="F9" s="44" t="n">
+        <v>1454.9</v>
+      </c>
+      <c r="G9" s="44" t="n">
+        <v>3239.1</v>
+      </c>
+      <c r="H9" s="44" t="n">
+        <v>3485.22</v>
+      </c>
+      <c r="I9" s="19">
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>GA4 paid-search sessions</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>11258</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>5717</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>12612</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>9984</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>5334</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>5937</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>4973</v>
+      </c>
+      <c r="I10" s="9">
+        <f>SUM(B10:H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Click-through rate</t>
+        </is>
+      </c>
+      <c r="B11" s="45">
+        <f>B7/B6</f>
+        <v/>
+      </c>
+      <c r="C11" s="45">
+        <f>C7/C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="45">
+        <f>D7/D6</f>
+        <v/>
+      </c>
+      <c r="E11" s="45">
+        <f>E7/E6</f>
+        <v/>
+      </c>
+      <c r="F11" s="45">
+        <f>F7/F6</f>
+        <v/>
+      </c>
+      <c r="G11" s="45">
+        <f>G7/G6</f>
+        <v/>
+      </c>
+      <c r="H11" s="45">
+        <f>H7/H6</f>
+        <v/>
+      </c>
+      <c r="I11" s="46">
+        <f>I7/I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Average cost per click</t>
+        </is>
+      </c>
+      <c r="B12" s="47">
+        <f>B8/B7</f>
+        <v/>
+      </c>
+      <c r="C12" s="47">
+        <f>C8/C7</f>
+        <v/>
+      </c>
+      <c r="D12" s="47">
+        <f>D8/D7</f>
+        <v/>
+      </c>
+      <c r="E12" s="47">
+        <f>E8/E7</f>
+        <v/>
+      </c>
+      <c r="F12" s="47">
+        <f>F8/F7</f>
+        <v/>
+      </c>
+      <c r="G12" s="47">
+        <f>G8/G7</f>
+        <v/>
+      </c>
+      <c r="H12" s="47">
+        <f>H8/H7</f>
+        <v/>
+      </c>
+      <c r="I12" s="48">
+        <f>I8/I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Cost per reported conversion</t>
+        </is>
+      </c>
+      <c r="B13" s="49">
+        <f>B8/B9</f>
+        <v/>
+      </c>
+      <c r="C13" s="49">
+        <f>C8/C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="49">
+        <f>D8/D9</f>
+        <v/>
+      </c>
+      <c r="E13" s="49">
+        <f>E8/E9</f>
+        <v/>
+      </c>
+      <c r="F13" s="49">
+        <f>F8/F9</f>
+        <v/>
+      </c>
+      <c r="G13" s="49">
+        <f>G8/G9</f>
+        <v/>
+      </c>
+      <c r="H13" s="49">
+        <f>H8/H9</f>
+        <v/>
+      </c>
+      <c r="I13" s="43">
+        <f>I8/I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>GA4 sessions per Google Ads click</t>
+        </is>
+      </c>
+      <c r="B14" s="50">
+        <f>B10/B7</f>
+        <v/>
+      </c>
+      <c r="C14" s="50">
+        <f>C10/C7</f>
+        <v/>
+      </c>
+      <c r="D14" s="50">
+        <f>D10/D7</f>
+        <v/>
+      </c>
+      <c r="E14" s="50">
+        <f>E10/E7</f>
+        <v/>
+      </c>
+      <c r="F14" s="50">
+        <f>F10/F7</f>
+        <v/>
+      </c>
+      <c r="G14" s="50">
+        <f>G10/G7</f>
+        <v/>
+      </c>
+      <c r="H14" s="50">
+        <f>H10/H7</f>
+        <v/>
+      </c>
+      <c r="I14" s="51">
+        <f>I10/I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>New patients (all sources)</t>
+        </is>
+      </c>
+      <c r="B15" s="25">
+        <f>Actuals!B12</f>
+        <v/>
+      </c>
+      <c r="C15" s="25">
+        <f>Actuals!C12</f>
+        <v/>
+      </c>
+      <c r="D15" s="25">
+        <f>Actuals!D12</f>
+        <v/>
+      </c>
+      <c r="E15" s="25">
+        <f>Actuals!E12</f>
+        <v/>
+      </c>
+      <c r="F15" s="25">
+        <f>Actuals!F12</f>
+        <v/>
+      </c>
+      <c r="G15" s="25">
+        <f>Actuals!G12</f>
+        <v/>
+      </c>
+      <c r="H15" s="25">
+        <f>Actuals!H12</f>
+        <v/>
+      </c>
+      <c r="I15" s="9">
+        <f>SUM(B15:H15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GA4 sessions per Google Ads click should sit near 0.8-0.9. It falls from 0.70 in January to 0.29 in July while clicks themselves stay flat —</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>that is GA4 losing the ability to record paid visits, not demand going away. This is the confirmation of FLAG 2 on the Digital Context tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Spend by service line</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Service line (from campaign name)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Ortho</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="n">
+        <v>73344.34</v>
+      </c>
+      <c r="C22" s="42" t="n">
+        <v>66874.78</v>
+      </c>
+      <c r="D22" s="42" t="n">
+        <v>176750.4</v>
+      </c>
+      <c r="E22" s="42" t="n">
+        <v>138406.84</v>
+      </c>
+      <c r="F22" s="42" t="n">
+        <v>100328.43</v>
+      </c>
+      <c r="G22" s="42" t="n">
+        <v>124006.65</v>
+      </c>
+      <c r="H22" s="42" t="n">
+        <v>132548.39</v>
+      </c>
+      <c r="I22" s="43">
+        <f>SUM(B22:H22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Spine</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="n">
+        <v>68091.19</v>
+      </c>
+      <c r="C23" s="42" t="n">
+        <v>42239.6</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <v>57095.26</v>
+      </c>
+      <c r="E23" s="42" t="n">
+        <v>60736.69</v>
+      </c>
+      <c r="F23" s="42" t="n">
+        <v>66329.98</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>107821.81</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>89047.48</v>
+      </c>
+      <c r="I23" s="43">
+        <f>SUM(B23:H23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="n">
+        <v>6257.23</v>
+      </c>
+      <c r="C24" s="42" t="n">
+        <v>11005.48</v>
+      </c>
+      <c r="D24" s="42" t="n">
+        <v>12673.66</v>
+      </c>
+      <c r="E24" s="42" t="n">
+        <v>12892.2</v>
+      </c>
+      <c r="F24" s="42" t="n">
+        <v>13978.66</v>
+      </c>
+      <c r="G24" s="42" t="n">
+        <v>17093.29</v>
+      </c>
+      <c r="H24" s="42" t="n">
+        <v>14048.26</v>
+      </c>
+      <c r="I24" s="43">
+        <f>SUM(B24:H24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="n">
+        <v>2394.35</v>
+      </c>
+      <c r="C25" s="42" t="n">
+        <v>2227.4</v>
+      </c>
+      <c r="D25" s="42" t="n">
+        <v>4971.03</v>
+      </c>
+      <c r="E25" s="42" t="n">
+        <v>6116.73</v>
+      </c>
+      <c r="F25" s="42" t="n">
+        <v>14117.7</v>
+      </c>
+      <c r="G25" s="42" t="n">
+        <v>18205.08</v>
+      </c>
+      <c r="H25" s="42" t="n">
+        <v>14970.97</v>
+      </c>
+      <c r="I25" s="43">
+        <f>SUM(B25:H25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Brand / other</t>
+        </is>
+      </c>
+      <c r="B26" s="42" t="n">
+        <v>19000.09</v>
+      </c>
+      <c r="C26" s="42" t="n">
+        <v>17646.93</v>
+      </c>
+      <c r="D26" s="42" t="n">
+        <v>32051.13</v>
+      </c>
+      <c r="E26" s="42" t="n">
+        <v>23388.84</v>
+      </c>
+      <c r="F26" s="42" t="n">
+        <v>17399</v>
+      </c>
+      <c r="G26" s="42" t="n">
+        <v>12322.14</v>
+      </c>
+      <c r="H26" s="42" t="n">
+        <v>11793.89</v>
+      </c>
+      <c r="I26" s="43">
+        <f>SUM(B26:H26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B27" s="52">
+        <f>SUM(B22:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="52">
+        <f>SUM(C22:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="52">
+        <f>SUM(D22:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="52">
+        <f>SUM(E22:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="52">
+        <f>SUM(F22:F26)</f>
+        <v/>
+      </c>
+      <c r="G27" s="52">
+        <f>SUM(G22:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="52">
+        <f>SUM(H22:H26)</f>
+        <v/>
+      </c>
+      <c r="I27" s="52">
+        <f>SUM(I22:I26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Campaigns are mapped to service lines by campaign name: Podiatry -&gt; Foot, "Neck, Back, Spine" and "Spine Conditions" -&gt; Spine,</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Orthopedic -&gt; Ortho, Hand -&gt; Hand, and Branded / Doctors / Port Huron / Auto Accident / Canadian Self Pay -&gt; Brand and other.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Port Huron is a location campaign covering several lines, so it sits in Brand and other rather than being split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Clicks by service line</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Service line (from campaign name)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Ortho</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>7959</v>
+      </c>
+      <c r="C35" s="15" t="n">
+        <v>6994</v>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>11069</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>8548</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>6161</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>6879</v>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>7115</v>
+      </c>
+      <c r="I35" s="9">
+        <f>SUM(B35:H35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Spine</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>3243</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>2503</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>3491</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>3037</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>3789</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>3222</v>
+      </c>
+      <c r="I36" s="9">
+        <f>SUM(B36:H36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="C37" s="15" t="n">
+        <v>1117</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>1172</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>1149</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>1266</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>1223</v>
+      </c>
+      <c r="I37" s="9">
+        <f>SUM(B37:H37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>686</v>
+      </c>
+      <c r="C38" s="15" t="n">
+        <v>604</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>1257</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>1169</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>1912</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>2348</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>2093</v>
+      </c>
+      <c r="I38" s="9">
+        <f>SUM(B38:H38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Brand / other</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>3539</v>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>3246</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>4012</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>4047</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>3544</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>3211</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>3291</v>
+      </c>
+      <c r="I39" s="9">
+        <f>SUM(B39:H39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
+        <f>SUM(B35:B39)</f>
+        <v/>
+      </c>
+      <c r="C40" s="11">
+        <f>SUM(C35:C39)</f>
+        <v/>
+      </c>
+      <c r="D40" s="11">
+        <f>SUM(D35:D39)</f>
+        <v/>
+      </c>
+      <c r="E40" s="11">
+        <f>SUM(E35:E39)</f>
+        <v/>
+      </c>
+      <c r="F40" s="11">
+        <f>SUM(F35:F39)</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>SUM(G35:G39)</f>
+        <v/>
+      </c>
+      <c r="H40" s="11">
+        <f>SUM(H35:H39)</f>
+        <v/>
+      </c>
+      <c r="I40" s="11">
+        <f>SUM(I35:I39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Reported conversions by service line</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Service line (from campaign name)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Ortho</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="n">
+        <v>730.89</v>
+      </c>
+      <c r="C44" s="44" t="n">
+        <v>487.45</v>
+      </c>
+      <c r="D44" s="44" t="n">
+        <v>885.51</v>
+      </c>
+      <c r="E44" s="44" t="n">
+        <v>757.78</v>
+      </c>
+      <c r="F44" s="44" t="n">
+        <v>549.11</v>
+      </c>
+      <c r="G44" s="44" t="n">
+        <v>1091.87</v>
+      </c>
+      <c r="H44" s="44" t="n">
+        <v>1330.7</v>
+      </c>
+      <c r="I44" s="19">
+        <f>SUM(B44:H44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Spine</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="n">
+        <v>216.06</v>
+      </c>
+      <c r="C45" s="44" t="n">
+        <v>115.82</v>
+      </c>
+      <c r="D45" s="44" t="n">
+        <v>221.03</v>
+      </c>
+      <c r="E45" s="44" t="n">
+        <v>192.65</v>
+      </c>
+      <c r="F45" s="44" t="n">
+        <v>162.94</v>
+      </c>
+      <c r="G45" s="44" t="n">
+        <v>418.47</v>
+      </c>
+      <c r="H45" s="44" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="I45" s="19">
+        <f>SUM(B45:H45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="B46" s="44" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="C46" s="44" t="n">
+        <v>60.99</v>
+      </c>
+      <c r="D46" s="44" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="E46" s="44" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="F46" s="44" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="G46" s="44" t="n">
+        <v>153.29</v>
+      </c>
+      <c r="H46" s="44" t="n">
+        <v>132.56</v>
+      </c>
+      <c r="I46" s="19">
+        <f>SUM(B46:H46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="n">
+        <v>78.98</v>
+      </c>
+      <c r="C47" s="44" t="n">
+        <v>40</v>
+      </c>
+      <c r="D47" s="44" t="n">
+        <v>140.57</v>
+      </c>
+      <c r="E47" s="44" t="n">
+        <v>139.82</v>
+      </c>
+      <c r="F47" s="44" t="n">
+        <v>212.47</v>
+      </c>
+      <c r="G47" s="44" t="n">
+        <v>320.05</v>
+      </c>
+      <c r="H47" s="44" t="n">
+        <v>355.16</v>
+      </c>
+      <c r="I47" s="19">
+        <f>SUM(B47:H47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Brand / other</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="n">
+        <v>414.91</v>
+      </c>
+      <c r="C48" s="44" t="n">
+        <v>424.19</v>
+      </c>
+      <c r="D48" s="44" t="n">
+        <v>645.59</v>
+      </c>
+      <c r="E48" s="44" t="n">
+        <v>511.72</v>
+      </c>
+      <c r="F48" s="44" t="n">
+        <v>463</v>
+      </c>
+      <c r="G48" s="44" t="n">
+        <v>1255.42</v>
+      </c>
+      <c r="H48" s="44" t="n">
+        <v>1293.13</v>
+      </c>
+      <c r="I48" s="19">
+        <f>SUM(B48:H48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B49" s="20">
+        <f>SUM(B44:B48)</f>
+        <v/>
+      </c>
+      <c r="C49" s="20">
+        <f>SUM(C44:C48)</f>
+        <v/>
+      </c>
+      <c r="D49" s="20">
+        <f>SUM(D44:D48)</f>
+        <v/>
+      </c>
+      <c r="E49" s="20">
+        <f>SUM(E44:E48)</f>
+        <v/>
+      </c>
+      <c r="F49" s="20">
+        <f>SUM(F44:F48)</f>
+        <v/>
+      </c>
+      <c r="G49" s="20">
+        <f>SUM(G44:G48)</f>
+        <v/>
+      </c>
+      <c r="H49" s="20">
+        <f>SUM(H44:H48)</f>
+        <v/>
+      </c>
+      <c r="I49" s="20">
+        <f>SUM(I44:I48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CAUTION: reported conversions roughly double in June across EVERY service line and nearly every campaign at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>A genuine performance gain does not arrive uniformly across unrelated campaigns in the same month. Treat June and July</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>conversion counts, and any cost-per-conversion built from them, as not comparable to January through May until the</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>conversion-action configuration change is confirmed with the paid agency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Does paid investment show up in actual new patients?</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Service line</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Spend Jan-26</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Spend Jul-26</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Spend change</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Clicks change</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>New patients Jan-26</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>New patients Jul-26</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>New patient change</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>YTD attainment vs budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Ortho</t>
+        </is>
+      </c>
+      <c r="B58" s="49">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="C58" s="49">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="D58" s="29">
+        <f>H22/B22-1</f>
+        <v/>
+      </c>
+      <c r="E58" s="29">
+        <f>H35/B35-1</f>
+        <v/>
+      </c>
+      <c r="F58" s="32">
+        <f>Actuals!B5</f>
+        <v/>
+      </c>
+      <c r="G58" s="32">
+        <f>Actuals!H5</f>
+        <v/>
+      </c>
+      <c r="H58" s="29">
+        <f>Actuals!H5/Actuals!B5-1</f>
+        <v/>
+      </c>
+      <c r="I58" s="23">
+        <f>'Perf to Budget'!I36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Spine</t>
+        </is>
+      </c>
+      <c r="B59" s="49">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="C59" s="49">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="D59" s="29">
+        <f>H23/B23-1</f>
+        <v/>
+      </c>
+      <c r="E59" s="29">
+        <f>H36/B36-1</f>
+        <v/>
+      </c>
+      <c r="F59" s="32">
+        <f>Actuals!B6</f>
+        <v/>
+      </c>
+      <c r="G59" s="32">
+        <f>Actuals!H6</f>
+        <v/>
+      </c>
+      <c r="H59" s="29">
+        <f>Actuals!H6/Actuals!B6-1</f>
+        <v/>
+      </c>
+      <c r="I59" s="23">
+        <f>'Perf to Budget'!I37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="B60" s="49">
+        <f>B24</f>
+        <v/>
+      </c>
+      <c r="C60" s="49">
+        <f>H24</f>
+        <v/>
+      </c>
+      <c r="D60" s="29">
+        <f>H24/B24-1</f>
+        <v/>
+      </c>
+      <c r="E60" s="29">
+        <f>H37/B37-1</f>
+        <v/>
+      </c>
+      <c r="F60" s="32">
+        <f>Actuals!B8</f>
+        <v/>
+      </c>
+      <c r="G60" s="32">
+        <f>Actuals!H8</f>
+        <v/>
+      </c>
+      <c r="H60" s="29">
+        <f>Actuals!H8/Actuals!B8-1</f>
+        <v/>
+      </c>
+      <c r="I60" s="23">
+        <f>'Perf to Budget'!I39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="B61" s="49">
+        <f>B25</f>
+        <v/>
+      </c>
+      <c r="C61" s="49">
+        <f>H25</f>
+        <v/>
+      </c>
+      <c r="D61" s="29">
+        <f>H25/B25-1</f>
+        <v/>
+      </c>
+      <c r="E61" s="29">
+        <f>H38/B38-1</f>
+        <v/>
+      </c>
+      <c r="F61" s="32">
+        <f>Actuals!B9</f>
+        <v/>
+      </c>
+      <c r="G61" s="32">
+        <f>Actuals!H9</f>
+        <v/>
+      </c>
+      <c r="H61" s="29">
+        <f>Actuals!H9/Actuals!B9-1</f>
+        <v/>
+      </c>
+      <c r="I61" s="23">
+        <f>'Perf to Budget'!I40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Foot maps to the Podiatry campaigns; the EMR service line is "Foot". Spend and click changes are January versus July.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>This is corroboration, not attribution. The EMR export carries no source field, so no new patient here is proven to have come from paid search.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A33:J33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6343,10 +7863,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Directional only. GA4 measures website behaviour; it does not attribute new patients. Read the data-quality flags first.</t>
-        </is>
-      </c>
-    </row>
+          <t>Directional only. GA4 measures website behaviour; it does not attribute new patients. See the Paid Media tab for the GA4 reconciliation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6371,21 +7892,21 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>FLAG 2  Sessions step down about 50% from late April onward and stay there — and the drop hits every channel at once, including</t>
+          <t>FLAG 2  CONFIRMED. Sessions step down about 50% from late April and stay there, across every channel at once. Google Ads</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Direct and Organic. A simultaneous, uniform, all-channel halving is the signature of a tracking or consent change, not of a</t>
+          <t xml:space="preserve">        clicks over the same months are flat (16,127 in January, 16,944 in July), and GA4 sessions per Ads click fall from</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        media decision. Verify against Google Search Console clicks and Google Ads before treating any May-July web number as real.</t>
+          <t xml:space="preserve">        0.70 to 0.29. The traffic did not go away; GA4 stopped recording it. Fix the tagging before using any May-July web number.</t>
         </is>
       </c>
     </row>
@@ -6417,6 +7938,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>

--- a/analytics/2026-new-patients-performance-to-budget.xlsx
+++ b/analytics/2026-new-patients-performance-to-budget.xlsx
@@ -7840,7 +7840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7892,21 +7892,21 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>FLAG 2  CONFIRMED. Sessions step down about 50% from late April and stay there, across every channel at once. Google Ads</t>
+          <t>FLAG 2  EXPLAINED. Sessions step down about 50% from late April and stay there, across every channel at once. SHP added a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        clicks over the same months are flat (16,127 in January, 16,944 in July), and GA4 sessions per Ads click fall from</t>
+          <t xml:space="preserve">        consent / opt-out widget to the website, which is the cause. Google Ads clicks over the same months are flat (16,127 in</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        0.70 to 0.29. The traffic did not go away; GA4 stopped recording it. Fix the tagging before using any May-July web number.</t>
+          <t xml:space="preserve">        January, 16,944 in July) while GA4 sessions per Ads click fall 0.70 -&gt; 0.29. Traffic did not fall; consented measurement did.</t>
         </is>
       </c>
     </row>
@@ -7927,270 +7927,132 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Bottom line: patient volume rose every month while measured web sessions fell by half. At least one of those two series is wrong,</t>
+          <t>FLAG 4  A consent / opt-out widget was added to the site. From late April GA4 records only about 29% of the visits Google Ads bills</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>and the patient data — counted from the EMR — is the one to trust.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t xml:space="preserve">        for, against roughly 70% in January. If that were purely visitors choosing to opt out it would mean a ~71% opt-out rate, which</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        is far above the 10-30% typical of a consent banner. Check whether the widget denies analytics by default or fires before the</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        visitor has chosen, rather than only on an explicit opt-out. Either way GA4 is now a sample, not a census.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>FLAG 5  The widget does not explain the 18 Feb - 1 Mar blackout, which predates it. That remains a separate, unexplained gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bottom line: patient volume rose every month while measured web sessions fell by half. The web series is the incomplete one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Until GA4 is re-baselined, use Google Ads clicks and Search Console clicks as the measure of traffic volume, and treat GA4 as</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>a directional read on behaviour among consented visitors only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>GA4 monthly summary</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Paid search sessions</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Organic search sessions</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Direct sessions</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Key events</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>New patients</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>New patients per 1,000 sessions</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Jan-26</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>21619</v>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>11258</v>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>6653</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>2482</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>3595</v>
-      </c>
-      <c r="G17" s="25">
-        <f>Actuals!B12</f>
-        <v/>
-      </c>
-      <c r="H17" s="28">
-        <f>G17/B17*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Feb-26</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>10893</v>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>5717</v>
-      </c>
-      <c r="D18" s="15" t="n">
-        <v>3499</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>1186</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>1774</v>
-      </c>
-      <c r="G18" s="25">
-        <f>Actuals!C12</f>
-        <v/>
-      </c>
-      <c r="H18" s="28">
-        <f>G18/B18*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Mar-26</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>21896</v>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>12612</v>
-      </c>
-      <c r="D19" s="15" t="n">
-        <v>6163</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>3298</v>
-      </c>
-      <c r="G19" s="25">
-        <f>Actuals!D12</f>
-        <v/>
-      </c>
-      <c r="H19" s="28">
-        <f>G19/B19*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Apr-26</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>17967</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>9984</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>5264</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>1717</v>
-      </c>
-      <c r="F20" s="15" t="n">
-        <v>2637</v>
-      </c>
-      <c r="G20" s="25">
-        <f>Actuals!E12</f>
-        <v/>
-      </c>
-      <c r="H20" s="28">
-        <f>G20/B20*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>May-26</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="n">
-        <v>9335</v>
-      </c>
-      <c r="C21" s="15" t="n">
-        <v>5334</v>
-      </c>
-      <c r="D21" s="15" t="n">
-        <v>3027</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>717</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>896</v>
-      </c>
-      <c r="G21" s="25">
-        <f>Actuals!F12</f>
-        <v/>
-      </c>
-      <c r="H21" s="28">
-        <f>G21/B21*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>10086</v>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>5937</v>
-      </c>
-      <c r="D22" s="15" t="n">
-        <v>3209</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>669</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>2177</v>
-      </c>
-      <c r="G22" s="25">
-        <f>Actuals!G12</f>
-        <v/>
-      </c>
-      <c r="H22" s="28">
-        <f>G22/B22*1000</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Jul-26</t>
+          <t>Jan-26</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
-        <v>8784</v>
+        <v>21619</v>
       </c>
       <c r="C23" s="15" t="n">
-        <v>4973</v>
+        <v>11258</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>2768</v>
+        <v>6653</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>594</v>
+        <v>2482</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>10398</v>
+        <v>3595</v>
       </c>
       <c r="G23" s="25">
-        <f>Actuals!H12</f>
+        <f>Actuals!B12</f>
         <v/>
       </c>
       <c r="H23" s="28">
@@ -8198,22 +8060,202 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>10893</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>5717</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>3499</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>1774</v>
+      </c>
+      <c r="G24" s="25">
+        <f>Actuals!C12</f>
+        <v/>
+      </c>
+      <c r="H24" s="28">
+        <f>G24/B24*1000</f>
+        <v/>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>21896</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>12612</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>6163</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>3298</v>
+      </c>
+      <c r="G25" s="25">
+        <f>Actuals!D12</f>
+        <v/>
+      </c>
+      <c r="H25" s="28">
+        <f>G25/B25*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>17967</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>9984</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>5264</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>1717</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>2637</v>
+      </c>
+      <c r="G26" s="25">
+        <f>Actuals!E12</f>
+        <v/>
+      </c>
+      <c r="H26" s="28">
+        <f>G26/B26*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>9335</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>5334</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>3027</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>717</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>896</v>
+      </c>
+      <c r="G27" s="25">
+        <f>Actuals!F12</f>
+        <v/>
+      </c>
+      <c r="H27" s="28">
+        <f>G27/B27*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>10086</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>5937</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>669</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>2177</v>
+      </c>
+      <c r="G28" s="25">
+        <f>Actuals!G12</f>
+        <v/>
+      </c>
+      <c r="H28" s="28">
+        <f>G28/B28*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>8784</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>4973</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>2768</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>594</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>10398</v>
+      </c>
+      <c r="G29" s="25">
+        <f>Actuals!H12</f>
+        <v/>
+      </c>
+      <c r="H29" s="28">
+        <f>G29/B29*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Source: GA4 property 370514163, sessionDefaultChannelGroup by yearMonth, pulled 2026-07-30. July covers 1-29 July only.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>"New patients per 1,000 sessions" is a ratio of two independent series, not a conversion rate. It rises sharply after April because</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>the denominator collapsed, which is exactly what FLAG 2 says not to trust.</t>
         </is>
@@ -8221,8 +8263,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:I15"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/analytics/2026-new-patients-performance-to-budget.xlsx
+++ b/analytics/2026-new-patients-performance-to-budget.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Trends" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Aug Scorecard" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Paid Media" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Digital Context" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Expense to Budget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Digital Context" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +24,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);-"/>
     <numFmt numFmtId="167" formatCode="+0.0%;-0.0%;0.0%"/>
     <numFmt numFmtId="168" formatCode="$#,##0"/>
     <numFmt numFmtId="169" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="$#,##0;($#,##0);-"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -148,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,6 +212,24 @@
     <xf numFmtId="2" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7840,6 +7860,588 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Marketing Expense to Budget — January through July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Budget from Marketing_Expense_Budget_2026.xlsx. Only Google Ads has verified actuals; every other line is plan, not spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Google Ads — the only line with verified actual spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>YTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="n">
+        <v>165000</v>
+      </c>
+      <c r="C6" s="53" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D6" s="53" t="n">
+        <v>185000</v>
+      </c>
+      <c r="E6" s="53" t="n">
+        <v>185000</v>
+      </c>
+      <c r="F6" s="53" t="n">
+        <v>185000</v>
+      </c>
+      <c r="G6" s="53" t="n">
+        <v>200000</v>
+      </c>
+      <c r="H6" s="53" t="n">
+        <v>200000</v>
+      </c>
+      <c r="I6" s="43">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Actual spend</t>
+        </is>
+      </c>
+      <c r="B7" s="53" t="n">
+        <v>169087.2</v>
+      </c>
+      <c r="C7" s="53" t="n">
+        <v>139994.19</v>
+      </c>
+      <c r="D7" s="53" t="n">
+        <v>283541.48</v>
+      </c>
+      <c r="E7" s="53" t="n">
+        <v>241541.3</v>
+      </c>
+      <c r="F7" s="53" t="n">
+        <v>212153.77</v>
+      </c>
+      <c r="G7" s="53" t="n">
+        <v>279448.97</v>
+      </c>
+      <c r="H7" s="53" t="n">
+        <v>262408.99</v>
+      </c>
+      <c r="I7" s="43">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Variance (over / under)</t>
+        </is>
+      </c>
+      <c r="B8" s="54">
+        <f>B7-B6</f>
+        <v/>
+      </c>
+      <c r="C8" s="54">
+        <f>C7-C6</f>
+        <v/>
+      </c>
+      <c r="D8" s="54">
+        <f>D7-D6</f>
+        <v/>
+      </c>
+      <c r="E8" s="54">
+        <f>E7-E6</f>
+        <v/>
+      </c>
+      <c r="F8" s="54">
+        <f>F7-F6</f>
+        <v/>
+      </c>
+      <c r="G8" s="54">
+        <f>G7-G6</f>
+        <v/>
+      </c>
+      <c r="H8" s="54">
+        <f>H7-H6</f>
+        <v/>
+      </c>
+      <c r="I8" s="54">
+        <f>I7-I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="B9" s="31">
+        <f>B7/B6-1</f>
+        <v/>
+      </c>
+      <c r="C9" s="31">
+        <f>C7/C6-1</f>
+        <v/>
+      </c>
+      <c r="D9" s="31">
+        <f>D7/D6-1</f>
+        <v/>
+      </c>
+      <c r="E9" s="31">
+        <f>E7/E6-1</f>
+        <v/>
+      </c>
+      <c r="F9" s="31">
+        <f>F7/F6-1</f>
+        <v/>
+      </c>
+      <c r="G9" s="31">
+        <f>G7/G6-1</f>
+        <v/>
+      </c>
+      <c r="H9" s="31">
+        <f>H7/H6-1</f>
+        <v/>
+      </c>
+      <c r="I9" s="31">
+        <f>I7/I6-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>July actual covers 1-30 July only (the export was pulled 30 July), so the July overspend is understated by roughly one day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads is 64% of the annual OpEx budget ($2,240,000 of $3,485,000), so its variance dominates the whole plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Total marketing budget — plan versus what can be verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Jan-Jul budget</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Jan-Jul actual</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Variance %</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Status of the actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Paid Search - Google</t>
+        </is>
+      </c>
+      <c r="B16" s="53" t="n">
+        <v>1285000</v>
+      </c>
+      <c r="C16" s="55">
+        <f>I7</f>
+        <v/>
+      </c>
+      <c r="D16" s="56">
+        <f>C16-B16</f>
+        <v/>
+      </c>
+      <c r="E16" s="29">
+        <f>C16/B16-1</f>
+        <v/>
+      </c>
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>Verified from the Google Ads export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>All other OpEx lines</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="n">
+        <v>720416.83</v>
+      </c>
+      <c r="C17" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED. No invoice or spend data supplied — budget shown as a placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>CapEx plan</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="n">
+        <v>158000</v>
+      </c>
+      <c r="C18" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>NOT VERIFIED. No spend data supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL Jan-Jul plan</t>
+        </is>
+      </c>
+      <c r="B19" s="52">
+        <f>SUM(B16:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+      <c r="E19" s="58" t="n"/>
+      <c r="F19" s="59" t="inlineStr">
+        <is>
+          <t>Cannot be closed out until the other lines are supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>If every non-Google line lands exactly on plan, Jan-Jul marketing OpEx is $2,308,593 against a $2,005,417 budget — 15.1% over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>At the July spend rate, Google Ads finishes 2026 at roughly $2,900,000 against a $2,240,000 full-year budget, about 30% over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Why the overspend happened — the CPA assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Assumption in the budget model</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Paid-search cost per new patient</t>
+        </is>
+      </c>
+      <c r="B26" s="60" t="inlineStr">
+        <is>
+          <t>$105</t>
+        </is>
+      </c>
+      <c r="C26" s="61">
+        <f>I7/Actuals!N12</f>
+        <v/>
+      </c>
+      <c r="D26" s="40" t="inlineStr">
+        <is>
+          <t>Actual divides ALL Google spend by ALL new patients from every source, so it flatters paid search and is still 2x the plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>New patients (annual)</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>14,400</t>
+        </is>
+      </c>
+      <c r="C27" s="62">
+        <f>Trends!F36</f>
+        <v/>
+      </c>
+      <c r="D27" s="40" t="inlineStr">
+        <is>
+          <t>Full-year projection at the current run rate, from the Trends tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Blended revenue per new patient</t>
+        </is>
+      </c>
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>$650</t>
+        </is>
+      </c>
+      <c r="C28" s="62" t="inlineStr">
+        <is>
+          <t>not verified</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="inlineStr">
+        <is>
+          <t>Finance owns this; no actual supplied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>The model derives spend from CPA. A $105 planned CPA against a real cost around double it is the arithmetic reason spend ran over</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>while patient volume ran under. Re-baselining that single input matters more than trimming any individual line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Errors found in the source budget model — fix before this plan is used again</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>The Patient_ROI tab is broken: every row returns #REF! or #VALUE!. It has produced no usable CPA or ROI number all year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>The Summary tab therefore shows #VALUE! for New Patients Forecast, Gap To Goal, Blended CPA, Direct ROI, and the B2C / PL splits —</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>which are exactly the board-facing figures the tab exists to report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Summary!B9 "Total CapEx (Annual)" reads 0, while the CapEx_Plan tab totals $208,000. The Summary understates capital spend by $208,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Inputs!B12 Social_Annual is $720,000, but OpEx_Monthly carries social at $18,000/month = $216,000/year. The input is not driving the schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>and the two disagree by $504,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Net effect: nobody could have read a correct CPA, ROI, or total spend figure out of this model at any point in 2026.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A14:J14"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B8:I9">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="4">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7867,7 +8469,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7980,7 +8581,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>

--- a/analytics/2026-new-patients-performance-to-budget.xlsx
+++ b/analytics/2026-new-patients-performance-to-budget.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Aug Scorecard" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Paid Media" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Expense to Budget" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Digital Context" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Capacity &amp; TAM" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Digital Context" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0);-"/>
@@ -32,6 +33,7 @@
     <numFmt numFmtId="168" formatCode="$#,##0"/>
     <numFmt numFmtId="169" formatCode="$#,##0.00"/>
     <numFmt numFmtId="170" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="171" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -150,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -230,6 +232,8 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="171" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -982,6 +986,440 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Digital Context — GA4, January through July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Directional only. GA4 measures website behaviour; it does not attribute new patients. See the Paid Media tab for the GA4 reconciliation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Data-quality flags — read before using any number on this tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>FLAG 1  GA4 recorded almost no traffic from 18 February to 1 March 2026 (single-digit sessions per day against a ~800/day baseline).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        February and early March web numbers are understated by roughly one week of traffic. Patient volume shows no matching dip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>FLAG 2  EXPLAINED. Sessions step down about 50% from late April and stay there, across every channel at once. SHP added a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        consent / opt-out widget to the website, which is the cause. Google Ads clicks over the same months are flat (16,127 in</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        January, 16,944 in July) while GA4 sessions per Ads click fall 0.70 -&gt; 0.29. Traffic did not fall; consented measurement did.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FLAG 3  July key events jump roughly 5x with no matching traffic increase, which means the key-event configuration changed in July.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Conversion counts are not comparable month to month across that break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>FLAG 4  A consent / opt-out widget was added to the site. From late April GA4 records only about 29% of the visits Google Ads bills</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        for, against roughly 70% in January. If that were purely visitors choosing to opt out it would mean a ~71% opt-out rate, which</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        is far above the 10-30% typical of a consent banner. Check whether the widget denies analytics by default or fires before the</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        visitor has chosen, rather than only on an explicit opt-out. Either way GA4 is now a sample, not a census.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>FLAG 5  The widget does not explain the 18 Feb - 1 Mar blackout, which predates it. That remains a separate, unexplained gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Bottom line: patient volume rose every month while measured web sessions fell by half. The web series is the incomplete one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Until GA4 is re-baselined, use Google Ads clicks and Search Console clicks as the measure of traffic volume, and treat GA4 as</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>a directional read on behaviour among consented visitors only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>GA4 monthly summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Paid search sessions</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Organic search sessions</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Direct sessions</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Key events</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>New patients</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>New patients per 1,000 sessions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Jan-26</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>21619</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>11258</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>6653</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>2482</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>3595</v>
+      </c>
+      <c r="G23" s="25">
+        <f>Actuals!B12</f>
+        <v/>
+      </c>
+      <c r="H23" s="28">
+        <f>G23/B23*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Feb-26</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>10893</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>5717</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>3499</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>1186</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>1774</v>
+      </c>
+      <c r="G24" s="25">
+        <f>Actuals!C12</f>
+        <v/>
+      </c>
+      <c r="H24" s="28">
+        <f>G24/B24*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Mar-26</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>21896</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>12612</v>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>6163</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>2145</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>3298</v>
+      </c>
+      <c r="G25" s="25">
+        <f>Actuals!D12</f>
+        <v/>
+      </c>
+      <c r="H25" s="28">
+        <f>G25/B25*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Apr-26</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>17967</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <v>9984</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>5264</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>1717</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>2637</v>
+      </c>
+      <c r="G26" s="25">
+        <f>Actuals!E12</f>
+        <v/>
+      </c>
+      <c r="H26" s="28">
+        <f>G26/B26*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>May-26</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>9335</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <v>5334</v>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>3027</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>717</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>896</v>
+      </c>
+      <c r="G27" s="25">
+        <f>Actuals!F12</f>
+        <v/>
+      </c>
+      <c r="H27" s="28">
+        <f>G27/B27*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Jun-26</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>10086</v>
+      </c>
+      <c r="C28" s="15" t="n">
+        <v>5937</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>3209</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>669</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>2177</v>
+      </c>
+      <c r="G28" s="25">
+        <f>Actuals!G12</f>
+        <v/>
+      </c>
+      <c r="H28" s="28">
+        <f>G28/B28*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Jul-26</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>8784</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <v>4973</v>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>2768</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>594</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>10398</v>
+      </c>
+      <c r="G29" s="25">
+        <f>Actuals!H12</f>
+        <v/>
+      </c>
+      <c r="H29" s="28">
+        <f>G29/B29*1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Source: GA4 property 370514163, sessionDefaultChannelGroup by yearMonth, pulled 2026-07-30. July covers 1-29 July only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>"New patients per 1,000 sessions" is a ratio of two independent series, not a conversion rate. It rises sharply after April because</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>the denominator collapsed, which is exactly what FLAG 2 says not to trust.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A21:I21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -8442,430 +8880,1171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Digital Context — GA4, January through July 2026</t>
+          <t>Clinic Capacity and Addressable Market — core service lines</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Directional only. GA4 measures website behaviour; it does not attribute new patients. See the Paid Media tab for the GA4 reconciliation.</t>
+          <t>Source: Clinic_Capacity_Dashboard_and_PA_Shuffle_Report, tab Sheet2, rows where IsFirst=1. Window 30 Mar - 30 Jul 2026, weekdays.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Data-quality flags — read before using any number on this tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>FLAG 1  GA4 recorded almost no traffic from 18 February to 1 March 2026 (single-digit sessions per day against a ~800/day baseline).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        February and early March web numbers are understated by roughly one week of traffic. Patient volume shows no matching dip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>FLAG 2  EXPLAINED. Sessions step down about 50% from late April and stay there, across every channel at once. SHP added a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        consent / opt-out widget to the website, which is the cause. Google Ads clicks over the same months are flat (16,127 in</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        January, 16,944 in July) while GA4 sessions per Ads click fall 0.70 -&gt; 0.29. Traffic did not fall; consented measurement did.</t>
+          <t>Assumptions — change these and everything below recalculates</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Annualisation factor</t>
+        </is>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>2.967479674796748</v>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>365 days / 123 days in the observed window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Realised new patients per booked slot</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="n">
+        <v>0.1246864922966679</v>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>EMR new patients 30 Mar-30 Jul (4,524) divided by booked core-line slots (36,283). Calibrated, not assumed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Practical maximum utilisation</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>Allows for cancellations, no-shows and schedule buffer. 100% is not an operating target.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>FLAG 3  July key events jump roughly 5x with no matching traffic increase, which means the key-event configuration changed in July.</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>The appointment file books 19.4% of visits as "New Patient", but only 12.5% of booked slots become a counted new patient in the EMR.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Conversion counts are not comparable month to month across that break.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>FLAG 4  A consent / opt-out widget was added to the site. From late April GA4 records only about 29% of the visits Google Ads bills</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>That 36% gap is cancellations, no-shows, and records excluded by the EMR export filters. It is a real number to investigate, not an error here.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        for, against roughly 70% in January. If that were purely visitors choosing to opt out it would mean a ~71% opt-out rate, which</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        is far above the 10-30% typical of a consent banner. Check whether the widget denies analytics by default or fires before the</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Addressable market inside existing physician clinic time — by service line</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Service line</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Slots available</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Slots booked</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Utilisation</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Unused slots</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Annual new-patient capacity at 100%</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Annual new patients at 90% utilisation</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Annual new patients at current rate</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Headroom to 90%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        visitor has chosen, rather than only on an explicit opt-out. Either way GA4 is now a sample, not a census.</t>
-        </is>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Spine</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>9889</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>6467</v>
+      </c>
+      <c r="D15" s="23">
+        <f>C15/B15</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>B15*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G15" s="32">
+        <f>B15*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H15" s="32">
+        <f>C15*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>G15-H15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>FLAG 5  The widget does not explain the 18 Feb - 1 Mar blackout, which predates it. That remains a separate, unexplained gap.</t>
-        </is>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Ortho</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>15400</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>12167</v>
+      </c>
+      <c r="D16" s="23">
+        <f>C16/B16</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>B16*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>B16*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>C16*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I16" s="21">
+        <f>G16-H16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Bottom line: patient volume rose every month while measured web sessions fell by half. The web series is the incomplete one.</t>
-        </is>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>8325</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>5873</v>
+      </c>
+      <c r="D17" s="23">
+        <f>C17/B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="32">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="F17" s="32">
+        <f>B17*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G17" s="32">
+        <f>B17*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H17" s="32">
+        <f>C17*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>G17-H17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Until GA4 is re-baselined, use Google Ads clicks and Search Console clicks as the measure of traffic volume, and treat GA4 as</t>
-        </is>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>10393</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>9348</v>
+      </c>
+      <c r="D18" s="23">
+        <f>C18/B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>B18*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G18" s="32">
+        <f>B18*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H18" s="32">
+        <f>C18*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>G18-H18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>a directional read on behaviour among consented visitors only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>GA4 monthly summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Sessions</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Paid search sessions</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Organic search sessions</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>Direct sessions</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Key events</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>New patients</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>New patients per 1,000 sessions</t>
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>2419</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D19" s="23">
+        <f>C19/B19</f>
+        <v/>
+      </c>
+      <c r="E19" s="32">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="F19" s="32">
+        <f>B19*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G19" s="32">
+        <f>B19*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H19" s="32">
+        <f>C19*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I19" s="21">
+        <f>G19-H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="11">
+        <f>SUM(B15:B19)</f>
+        <v/>
+      </c>
+      <c r="C20" s="11">
+        <f>SUM(C15:C19)</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>C20/B20</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>SUM(E15:E19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="11">
+        <f>SUM(F15:F19)</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>SUM(G15:G19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="11">
+        <f>SUM(H15:H19)</f>
+        <v/>
+      </c>
+      <c r="I20" s="22">
+        <f>G20-H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Read the headroom column as: additional new patients per year available from clinic time these physicians ALREADY have on the schedule.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Jan-26</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="n">
-        <v>21619</v>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>11258</v>
-      </c>
-      <c r="D23" s="15" t="n">
-        <v>6653</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>2482</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>3595</v>
-      </c>
-      <c r="G23" s="25">
-        <f>Actuals!B12</f>
-        <v/>
-      </c>
-      <c r="H23" s="28">
-        <f>G23/B23*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Feb-26</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>10893</v>
-      </c>
-      <c r="C24" s="15" t="n">
-        <v>5717</v>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>3499</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>1186</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>1774</v>
-      </c>
-      <c r="G24" s="25">
-        <f>Actuals!C12</f>
-        <v/>
-      </c>
-      <c r="H24" s="28">
-        <f>G24/B24*1000</f>
-        <v/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>It requires no new hires, no new sites and no additional marketing reach — only filling sessions that are already being offered.</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Mar-26</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>21896</v>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>12612</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>6163</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>2145</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>3298</v>
-      </c>
-      <c r="G25" s="25">
-        <f>Actuals!D12</f>
-        <v/>
-      </c>
-      <c r="H25" s="28">
-        <f>G25/B25*1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Apr-26</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>17967</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>9984</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>5264</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>1717</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>2637</v>
-      </c>
-      <c r="G26" s="25">
-        <f>Actuals!E12</f>
-        <v/>
-      </c>
-      <c r="H26" s="28">
-        <f>G26/B26*1000</f>
-        <v/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Addressable market by hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Hub</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Slots available</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Slots booked</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Utilisation</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Unused slots</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Annual new-patient capacity at 100%</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Annual new patients at 90% utilisation</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Annual new patients at current rate</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Headroom to 90%</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>May-26</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>9335</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>5334</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>3027</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>717</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>896</v>
-      </c>
-      <c r="G27" s="25">
-        <f>Actuals!F12</f>
-        <v/>
-      </c>
-      <c r="H27" s="28">
-        <f>G27/B27*1000</f>
+          <t>Sterling Heights</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>16531</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>12506</v>
+      </c>
+      <c r="D27" s="23">
+        <f>C27/B27</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>B27*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G27" s="32">
+        <f>B27*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H27" s="32">
+        <f>C27*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I27" s="21">
+        <f>G27-H27</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Jun-26</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>10086</v>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>5937</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>3209</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>669</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>2177</v>
-      </c>
-      <c r="G28" s="25">
-        <f>Actuals!G12</f>
-        <v/>
-      </c>
-      <c r="H28" s="28">
-        <f>G28/B28*1000</f>
+          <t>Southfield</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>6794</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>4574</v>
+      </c>
+      <c r="D28" s="23">
+        <f>C28/B28</f>
+        <v/>
+      </c>
+      <c r="E28" s="32">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="F28" s="32">
+        <f>B28*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G28" s="32">
+        <f>B28*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H28" s="32">
+        <f>C28*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I28" s="21">
+        <f>G28-H28</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Jul-26</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>8784</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>4973</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>2768</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>594</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>10398</v>
-      </c>
-      <c r="G29" s="25">
-        <f>Actuals!H12</f>
-        <v/>
-      </c>
-      <c r="H29" s="28">
-        <f>G29/B29*1000</f>
+          <t>Livonia</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>20512</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>17354</v>
+      </c>
+      <c r="D29" s="23">
+        <f>C29/B29</f>
+        <v/>
+      </c>
+      <c r="E29" s="32">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="F29" s="32">
+        <f>B29*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G29" s="32">
+        <f>B29*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H29" s="32">
+        <f>C29*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I29" s="21">
+        <f>G29-H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Port Huron</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>1609</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D30" s="23">
+        <f>C30/B30</f>
+        <v/>
+      </c>
+      <c r="E30" s="32">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="F30" s="32">
+        <f>B30*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G30" s="32">
+        <f>B30*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H30" s="32">
+        <f>C30*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I30" s="21">
+        <f>G30-H30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Source: GA4 property 370514163, sessionDefaultChannelGroup by yearMonth, pulled 2026-07-30. July covers 1-29 July only.</t>
-        </is>
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>980</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="D31" s="23">
+        <f>C31/B31</f>
+        <v/>
+      </c>
+      <c r="E31" s="32">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="F31" s="32">
+        <f>B31*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G31" s="32">
+        <f>B31*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H31" s="32">
+        <f>C31*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I31" s="21">
+        <f>G31-H31</f>
+        <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>"New patients per 1,000 sessions" is a ratio of two independent series, not a conversion rate. It rises sharply after April because</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>the denominator collapsed, which is exactly what FLAG 2 says not to trust.</t>
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>SUM(B27:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="11">
+        <f>SUM(C27:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="24">
+        <f>C32/B32</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>SUM(E27:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
+        <f>SUM(F27:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
+        <f>SUM(G27:G31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="11">
+        <f>SUM(H27:H31)</f>
+        <v/>
+      </c>
+      <c r="I32" s="22">
+        <f>G32-H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Livonia is effectively full at 85%. Sterling Heights and Southfield hold nearly three quarters of the total headroom between them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Why Friday is light — capacity offered, not demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Clinic days observed</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Provider-sessions per day</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Slots offered per day</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Slots booked per day</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Utilisation</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Unused slots per day</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C38" s="28" t="n">
+        <v>18.55555555555556</v>
+      </c>
+      <c r="D38" s="32" t="n">
+        <v>581.4444444444445</v>
+      </c>
+      <c r="E38" s="32" t="n">
+        <v>432.3333333333333</v>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>0.7435505446206765</v>
+      </c>
+      <c r="G38" s="32" t="n">
+        <v>149.1111111111111</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C39" s="28" t="n">
+        <v>17.77777777777778</v>
+      </c>
+      <c r="D39" s="32" t="n">
+        <v>601.5</v>
+      </c>
+      <c r="E39" s="32" t="n">
+        <v>510.2222222222222</v>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>0.848249746005357</v>
+      </c>
+      <c r="G39" s="32" t="n">
+        <v>91.27777777777777</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="28" t="n">
+        <v>22.05555555555556</v>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>558.5</v>
+      </c>
+      <c r="E40" s="32" t="n">
+        <v>428.3888888888889</v>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>0.7670347160051726</v>
+      </c>
+      <c r="G40" s="32" t="n">
+        <v>130.1111111111111</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C41" s="28" t="n">
+        <v>19.22222222222222</v>
+      </c>
+      <c r="D41" s="32" t="n">
+        <v>551.1666666666666</v>
+      </c>
+      <c r="E41" s="32" t="n">
+        <v>423.7222222222222</v>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>0.7687733091422235</v>
+      </c>
+      <c r="G41" s="32" t="n">
+        <v>127.4444444444444</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>12.11764705882353</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>303.4705882352941</v>
+      </c>
+      <c r="E42" s="32" t="n">
+        <v>234.0588235294118</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>0.7712735026167862</v>
+      </c>
+      <c r="G42" s="32" t="n">
+        <v>69.41176470588235</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Friday utilisation (77%) matches Wednesday and Thursday and beats Monday. Friday clinics fill perfectly well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Friday simply offers 45% fewer slots and runs a third fewer provider-sessions. The light Friday is a scheduling decision, not weak demand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Scenario — staffing Friday like Thursday</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Measure</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Extra slots per Friday</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>247.6960784313725</v>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>Thursday slots per day less Friday slots per day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Friday fill rate applied</t>
+        </is>
+      </c>
+      <c r="B50" s="64" t="n">
+        <v>0.7712735026167862</v>
+      </c>
+      <c r="C50" s="36" t="inlineStr">
+        <is>
+          <t>Fridays already fill at this rate, so new Friday slots are assumed to fill the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Extra new patients per Friday</t>
+        </is>
+      </c>
+      <c r="B51" s="19">
+        <f>B49*B50*$B$7</f>
+        <v/>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>Extra slots x fill rate x realised new patients per booked slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Fridays per year</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C52" s="36" t="inlineStr">
+        <is>
+          <t>Allows for holidays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Extra new patients per year</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>B51*B52</f>
+        <v/>
+      </c>
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>The prize for putting more physician time into Fridays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>What the whole picture adds up to</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Ceiling</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>New patients per year</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>What it assumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026 budget</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>Budget!N12</f>
+        <v/>
+      </c>
+      <c r="C57" s="40" t="inlineStr">
+        <is>
+          <t>The plan as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Current run rate</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>H20</f>
+        <v/>
+      </c>
+      <c r="C58" s="40" t="inlineStr">
+        <is>
+          <t>Core service lines at the 30 Mar - 30 Jul booking rate, annualised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Fill existing schedule to 90%</t>
+        </is>
+      </c>
+      <c r="B59" s="9">
+        <f>G20</f>
+        <v/>
+      </c>
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>No new physicians, no new sites, no extra marketing reach. Fill sessions already offered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Plus Friday staffed like Thursday</t>
+        </is>
+      </c>
+      <c r="B60" s="9">
+        <f>G20+B53</f>
+        <v/>
+      </c>
+      <c r="C60" s="40" t="inlineStr">
+        <is>
+          <t>Adds physician time on Fridays at the fill rate Fridays already achieve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Absolute ceiling of current schedule</t>
+        </is>
+      </c>
+      <c r="B61" s="9">
+        <f>F20</f>
+        <v/>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>100% utilisation. Not an operating target — shown as the hard boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>The headline: the 2026 budget sits BELOW the ceiling of the clinic time these physicians are already offering. The plan is reachable</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>without hiring, provided utilisation moves from 78% to 90% — and Spine, Southfield and Sterling Heights are where that slack sits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Caveat: this measures appointment slots, not operating-room time, imaging, staffing ratios or payer mix. Ops owns those constraints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Limits of this analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Window is 30 March to 30 July 2026 only. Earlier months are not in the capacity file, so seasonality is not captured.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Slot counts come from the published schedule. A slot that exists in the template but that a provider never intended to work still counts as available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Service line is taken from the file’s own Lookup tab. PENS, X-ray, MA, PA and PCP are excluded as non-core at your direction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Booked-to-realised conversion is a single blended factor. It almost certainly varies by line and hub; splitting it would sharpen every number here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>This is a supply-side market size. It says what the current schedule can hold, not what the surrounding population demands.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="7">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A21:I21"/>
   </mergeCells>
+  <conditionalFormatting sqref="D15:D20">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
+      <formula>0.75</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D27:D32">
+    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="4">
+      <formula>0.75</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="greaterThanOrEqual" dxfId="5">
+      <formula>0.9</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/analytics/2026-new-patients-performance-to-budget.xlsx
+++ b/analytics/2026-new-patients-performance-to-budget.xlsx
@@ -152,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +188,7 @@
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4525,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5731,31 +5732,165 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Full-year scenarios — the run rate is rising, so a flat projection understates it</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Aug-Dec per operating day</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Aug-Dec new patients</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>FY 2026 total</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>vs budget</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Attainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Flat at the May-July average</t>
+        </is>
+      </c>
+      <c r="B40" s="28">
+        <f>B36</f>
+        <v/>
+      </c>
+      <c r="C40" s="32">
+        <f>B40*C36</f>
+        <v/>
+      </c>
+      <c r="D40" s="9">
+        <f>C40+E36</f>
+        <v/>
+      </c>
+      <c r="E40" s="21">
+        <f>D40-G36</f>
+        <v/>
+      </c>
+      <c r="F40" s="27">
+        <f>D40/G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Flat at July</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="n">
+        <v>53.545</v>
+      </c>
+      <c r="C41" s="32">
+        <f>B41*C36</f>
+        <v/>
+      </c>
+      <c r="D41" s="9">
+        <f>C41+E36</f>
+        <v/>
+      </c>
+      <c r="E41" s="21">
+        <f>D41-G36</f>
+        <v/>
+      </c>
+      <c r="F41" s="27">
+        <f>D41/G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Apr-Jul trend continues</t>
+        </is>
+      </c>
+      <c r="B42" s="28">
+        <f>(48.18+1.394*7)</f>
+        <v/>
+      </c>
+      <c r="C42" s="32">
+        <f>B42*C36</f>
+        <v/>
+      </c>
+      <c r="D42" s="9">
+        <f>C42+E36</f>
+        <v/>
+      </c>
+      <c r="E42" s="21">
+        <f>D42-G36</f>
+        <v/>
+      </c>
+      <c r="F42" s="27">
+        <f>D42/G36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>The trend row uses the mean Aug-Dec per-day from a linear fit to April-July. Extrapolating five months is optimistic — treat it as the</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>upper end, not a forecast. All three scenarios still land short of budget on volume alone; closing the rest needs the mix shift on Capacity &amp; TAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Run rate = May-July actual per operating day, the most recent and most representative three months. It carries no seasonality adjustment.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Aug-Dec operating days come from the Actuals tab, row 14. Correct them for your real clinic calendar and this projection updates.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>The budget is materially front-half weighted (Mar, Apr and Jun are the three largest budgeted months); actual volume has instead built steadily through the year.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A38:J38"/>
   </mergeCells>
   <conditionalFormatting sqref="M19:M25">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
@@ -5837,19 +5972,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33">
+      <c r="A6" s="34">
         <f>Budget!I12</f>
         <v/>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>E17</f>
         <v/>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>F17</f>
         <v/>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="35">
         <f>Actuals!I14</f>
         <v/>
       </c>
@@ -5925,7 +6060,7 @@
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>MAX(B11,E11)</f>
         <v/>
       </c>
@@ -5960,7 +6095,7 @@
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="36">
         <f>MAX(B12,E12)</f>
         <v/>
       </c>
@@ -5995,7 +6130,7 @@
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="36">
         <f>MAX(B13,E13)</f>
         <v/>
       </c>
@@ -6030,7 +6165,7 @@
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>MAX(B14,E14)</f>
         <v/>
       </c>
@@ -6065,7 +6200,7 @@
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>MAX(B15,E15)</f>
         <v/>
       </c>
@@ -6100,7 +6235,7 @@
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="36">
         <f>MAX(B16,E16)</f>
         <v/>
       </c>
@@ -6196,7 +6331,7 @@
         <f>B17</f>
         <v/>
       </c>
-      <c r="C24" s="36" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Hits the August budget of roughly 1,260 new patients.</t>
         </is>
@@ -6212,7 +6347,7 @@
         <f>E17</f>
         <v/>
       </c>
-      <c r="C25" s="36" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Holds the May-July run rate. Real progress, still short of budget.</t>
         </is>
@@ -6228,7 +6363,7 @@
         <f>E17*0.95</f>
         <v/>
       </c>
-      <c r="C26" s="36" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>More than 5% below the current run rate; the seven-month improvement has stalled.</t>
         </is>
@@ -6289,7 +6424,7 @@
           <t>Week 1</t>
         </is>
       </c>
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>Aug 3-7</t>
         </is>
@@ -6321,7 +6456,7 @@
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Aug 10-14</t>
         </is>
@@ -6353,7 +6488,7 @@
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>Aug 17-21</t>
         </is>
@@ -6385,7 +6520,7 @@
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>Aug 24-28</t>
         </is>
@@ -6417,7 +6552,7 @@
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>Aug 31</t>
         </is>
@@ -6490,7 +6625,7 @@
           <t>B2C + natural demand</t>
         </is>
       </c>
-      <c r="B39" s="37">
+      <c r="B39" s="38">
         <f>Budget!I27/(Budget!I$27+Budget!I$28)</f>
         <v/>
       </c>
@@ -6498,12 +6633,12 @@
         <f>$F$17*B39</f>
         <v/>
       </c>
-      <c r="D39" s="38" t="inlineStr">
+      <c r="D39" s="39" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="E39" s="36" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>Paid and organic demand hold; the web measurement break is fixed so we can see it.</t>
         </is>
@@ -6515,7 +6650,7 @@
           <t>B2B referral / liaison</t>
         </is>
       </c>
-      <c r="B40" s="37">
+      <c r="B40" s="38">
         <f>Budget!I28/(Budget!I$27+Budget!I$28)</f>
         <v/>
       </c>
@@ -6523,12 +6658,12 @@
         <f>$F$17*B40</f>
         <v/>
       </c>
-      <c r="D40" s="38" t="inlineStr">
+      <c r="D40" s="39" t="inlineStr">
         <is>
           <t>Physician liaison</t>
         </is>
       </c>
-      <c r="E40" s="36" t="inlineStr">
+      <c r="E40" s="37" t="inlineStr">
         <is>
           <t>Referral volume from target accounts is captured and attributed in the EMR.</t>
         </is>
@@ -6576,189 +6711,189 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="39" t="inlineStr">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>New patients booked per operating day</t>
         </is>
       </c>
-      <c r="B46" s="40" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>EMR export</t>
         </is>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>The single number this scorecard grades.</t>
         </is>
       </c>
-      <c r="D46" s="41" t="inlineStr">
+      <c r="D46" s="42" t="inlineStr">
         <is>
           <t>At or above 53.5</t>
         </is>
       </c>
-      <c r="E46" s="41" t="inlineStr">
+      <c r="E46" s="42" t="inlineStr">
         <is>
           <t>Practice ops</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="39" t="inlineStr">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>Website sessions per weekday</t>
         </is>
       </c>
-      <c r="B47" s="40" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>GA4 property 370514163</t>
         </is>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>Leading demand signal — but see the measurement break flagged on Digital Context.</t>
         </is>
       </c>
-      <c r="D47" s="41" t="inlineStr">
+      <c r="D47" s="42" t="inlineStr">
         <is>
           <t>Restore reporting first</t>
         </is>
       </c>
-      <c r="E47" s="41" t="inlineStr">
+      <c r="E47" s="42" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>Paid search sessions</t>
         </is>
       </c>
-      <c r="B48" s="40" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>GA4 / Google Ads</t>
         </is>
       </c>
-      <c r="C48" s="40" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>Largest single acquisition channel by session volume all year.</t>
         </is>
       </c>
-      <c r="D48" s="41" t="inlineStr">
+      <c r="D48" s="42" t="inlineStr">
         <is>
           <t>Stable or rising</t>
         </is>
       </c>
-      <c r="E48" s="41" t="inlineStr">
+      <c r="E48" s="42" t="inlineStr">
         <is>
           <t>Paid agency</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
+      <c r="A49" s="40" t="inlineStr">
         <is>
           <t>Spine new patients per operating day</t>
         </is>
       </c>
-      <c r="B49" s="40" t="inlineStr">
+      <c r="B49" s="41" t="inlineStr">
         <is>
           <t>EMR export</t>
         </is>
       </c>
-      <c r="C49" s="40" t="inlineStr">
+      <c r="C49" s="41" t="inlineStr">
         <is>
           <t>Worst variance to budget of any line at 74.9% YTD.</t>
         </is>
       </c>
-      <c r="D49" s="41" t="inlineStr">
+      <c r="D49" s="42" t="inlineStr">
         <is>
           <t>At or above 11.2</t>
         </is>
       </c>
-      <c r="E49" s="41" t="inlineStr">
+      <c r="E49" s="42" t="inlineStr">
         <is>
           <t>Spine service line</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
+      <c r="A50" s="40" t="inlineStr">
         <is>
           <t>Pain new patients per operating day</t>
         </is>
       </c>
-      <c r="B50" s="40" t="inlineStr">
+      <c r="B50" s="41" t="inlineStr">
         <is>
           <t>EMR export</t>
         </is>
       </c>
-      <c r="C50" s="40" t="inlineStr">
+      <c r="C50" s="41" t="inlineStr">
         <is>
           <t>Lowest attainment of any line at 60.1% YTD.</t>
         </is>
       </c>
-      <c r="D50" s="41" t="inlineStr">
+      <c r="D50" s="42" t="inlineStr">
         <is>
           <t>At or above 3.5</t>
         </is>
       </c>
-      <c r="E50" s="41" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>Pain service line</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="39" t="inlineStr">
+      <c r="A51" s="40" t="inlineStr">
         <is>
           <t>Referral volume from target accounts</t>
         </is>
       </c>
-      <c r="B51" s="40" t="inlineStr">
+      <c r="B51" s="41" t="inlineStr">
         <is>
           <t>Liaison CRM</t>
         </is>
       </c>
-      <c r="C51" s="40" t="inlineStr">
+      <c r="C51" s="41" t="inlineStr">
         <is>
           <t>21.4% of the budget is assumed to come from B2B and is currently unmeasured.</t>
         </is>
       </c>
-      <c r="D51" s="41" t="inlineStr">
+      <c r="D51" s="42" t="inlineStr">
         <is>
           <t>Baseline it in August</t>
         </is>
       </c>
-      <c r="E51" s="41" t="inlineStr">
+      <c r="E51" s="42" t="inlineStr">
         <is>
           <t>Physician liaison</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="39" t="inlineStr">
+      <c r="A52" s="40" t="inlineStr">
         <is>
           <t>Primary Care new patients</t>
         </is>
       </c>
-      <c r="B52" s="40" t="inlineStr">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>EMR export</t>
         </is>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C52" s="41" t="inlineStr">
         <is>
           <t>Fell from 53 in January to 16 in July; a real decline, not a rounding issue.</t>
         </is>
       </c>
-      <c r="D52" s="41" t="inlineStr">
+      <c r="D52" s="42" t="inlineStr">
         <is>
           <t>Diagnose before target</t>
         </is>
       </c>
-      <c r="E52" s="41" t="inlineStr">
+      <c r="E52" s="42" t="inlineStr">
         <is>
           <t>PCP service line</t>
         </is>
@@ -6949,28 +7084,28 @@
           <t>Cost</t>
         </is>
       </c>
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="43" t="n">
         <v>169087.2</v>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="43" t="n">
         <v>139994.19</v>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D8" s="43" t="n">
         <v>283541.48</v>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="43" t="n">
         <v>241541.3</v>
       </c>
-      <c r="F8" s="42" t="n">
+      <c r="F8" s="43" t="n">
         <v>212153.77</v>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="43" t="n">
         <v>279448.97</v>
       </c>
-      <c r="H8" s="42" t="n">
+      <c r="H8" s="43" t="n">
         <v>262408.99</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="44">
         <f>SUM(B8:H8)</f>
         <v/>
       </c>
@@ -6981,25 +7116,25 @@
           <t>Reported conversions</t>
         </is>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="45" t="n">
         <v>1484.87</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="45" t="n">
         <v>1128.45</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="45" t="n">
         <v>1980.88</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="45" t="n">
         <v>1682.11</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="45" t="n">
         <v>1454.9</v>
       </c>
-      <c r="G9" s="44" t="n">
+      <c r="G9" s="45" t="n">
         <v>3239.1</v>
       </c>
-      <c r="H9" s="44" t="n">
+      <c r="H9" s="45" t="n">
         <v>3485.22</v>
       </c>
       <c r="I9" s="19">
@@ -7045,35 +7180,35 @@
           <t>Click-through rate</t>
         </is>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="46">
         <f>B7/B6</f>
         <v/>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="46">
         <f>C7/C6</f>
         <v/>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="46">
         <f>D7/D6</f>
         <v/>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="46">
         <f>E7/E6</f>
         <v/>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="46">
         <f>F7/F6</f>
         <v/>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="46">
         <f>G7/G6</f>
         <v/>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="46">
         <f>H7/H6</f>
         <v/>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="47">
         <f>I7/I6</f>
         <v/>
       </c>
@@ -7084,35 +7219,35 @@
           <t>Average cost per click</t>
         </is>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="48">
         <f>B8/B7</f>
         <v/>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="48">
         <f>C8/C7</f>
         <v/>
       </c>
-      <c r="D12" s="47">
+      <c r="D12" s="48">
         <f>D8/D7</f>
         <v/>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>E8/E7</f>
         <v/>
       </c>
-      <c r="F12" s="47">
+      <c r="F12" s="48">
         <f>F8/F7</f>
         <v/>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="48">
         <f>G8/G7</f>
         <v/>
       </c>
-      <c r="H12" s="47">
+      <c r="H12" s="48">
         <f>H8/H7</f>
         <v/>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="49">
         <f>I8/I7</f>
         <v/>
       </c>
@@ -7123,35 +7258,35 @@
           <t>Cost per reported conversion</t>
         </is>
       </c>
-      <c r="B13" s="49">
+      <c r="B13" s="50">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C13" s="49">
+      <c r="C13" s="50">
         <f>C8/C9</f>
         <v/>
       </c>
-      <c r="D13" s="49">
+      <c r="D13" s="50">
         <f>D8/D9</f>
         <v/>
       </c>
-      <c r="E13" s="49">
+      <c r="E13" s="50">
         <f>E8/E9</f>
         <v/>
       </c>
-      <c r="F13" s="49">
+      <c r="F13" s="50">
         <f>F8/F9</f>
         <v/>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="50">
         <f>G8/G9</f>
         <v/>
       </c>
-      <c r="H13" s="49">
+      <c r="H13" s="50">
         <f>H8/H9</f>
         <v/>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="44">
         <f>I8/I9</f>
         <v/>
       </c>
@@ -7162,35 +7297,35 @@
           <t>GA4 sessions per Google Ads click</t>
         </is>
       </c>
-      <c r="B14" s="50">
+      <c r="B14" s="51">
         <f>B10/B7</f>
         <v/>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="51">
         <f>C10/C7</f>
         <v/>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="51">
         <f>D10/D7</f>
         <v/>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="51">
         <f>E10/E7</f>
         <v/>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="51">
         <f>F10/F7</f>
         <v/>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="51">
         <f>G10/G7</f>
         <v/>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="51">
         <f>H10/H7</f>
         <v/>
       </c>
-      <c r="I14" s="51">
+      <c r="I14" s="52">
         <f>I10/I7</f>
         <v/>
       </c>
@@ -7308,28 +7443,28 @@
           <t>Ortho</t>
         </is>
       </c>
-      <c r="B22" s="42" t="n">
+      <c r="B22" s="43" t="n">
         <v>73344.34</v>
       </c>
-      <c r="C22" s="42" t="n">
+      <c r="C22" s="43" t="n">
         <v>66874.78</v>
       </c>
-      <c r="D22" s="42" t="n">
+      <c r="D22" s="43" t="n">
         <v>176750.4</v>
       </c>
-      <c r="E22" s="42" t="n">
+      <c r="E22" s="43" t="n">
         <v>138406.84</v>
       </c>
-      <c r="F22" s="42" t="n">
+      <c r="F22" s="43" t="n">
         <v>100328.43</v>
       </c>
-      <c r="G22" s="42" t="n">
+      <c r="G22" s="43" t="n">
         <v>124006.65</v>
       </c>
-      <c r="H22" s="42" t="n">
+      <c r="H22" s="43" t="n">
         <v>132548.39</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="44">
         <f>SUM(B22:H22)</f>
         <v/>
       </c>
@@ -7340,28 +7475,28 @@
           <t>Spine</t>
         </is>
       </c>
-      <c r="B23" s="42" t="n">
+      <c r="B23" s="43" t="n">
         <v>68091.19</v>
       </c>
-      <c r="C23" s="42" t="n">
+      <c r="C23" s="43" t="n">
         <v>42239.6</v>
       </c>
-      <c r="D23" s="42" t="n">
+      <c r="D23" s="43" t="n">
         <v>57095.26</v>
       </c>
-      <c r="E23" s="42" t="n">
+      <c r="E23" s="43" t="n">
         <v>60736.69</v>
       </c>
-      <c r="F23" s="42" t="n">
+      <c r="F23" s="43" t="n">
         <v>66329.98</v>
       </c>
-      <c r="G23" s="42" t="n">
+      <c r="G23" s="43" t="n">
         <v>107821.81</v>
       </c>
-      <c r="H23" s="42" t="n">
+      <c r="H23" s="43" t="n">
         <v>89047.48</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="44">
         <f>SUM(B23:H23)</f>
         <v/>
       </c>
@@ -7372,28 +7507,28 @@
           <t>Foot</t>
         </is>
       </c>
-      <c r="B24" s="42" t="n">
+      <c r="B24" s="43" t="n">
         <v>6257.23</v>
       </c>
-      <c r="C24" s="42" t="n">
+      <c r="C24" s="43" t="n">
         <v>11005.48</v>
       </c>
-      <c r="D24" s="42" t="n">
+      <c r="D24" s="43" t="n">
         <v>12673.66</v>
       </c>
-      <c r="E24" s="42" t="n">
+      <c r="E24" s="43" t="n">
         <v>12892.2</v>
       </c>
-      <c r="F24" s="42" t="n">
+      <c r="F24" s="43" t="n">
         <v>13978.66</v>
       </c>
-      <c r="G24" s="42" t="n">
+      <c r="G24" s="43" t="n">
         <v>17093.29</v>
       </c>
-      <c r="H24" s="42" t="n">
+      <c r="H24" s="43" t="n">
         <v>14048.26</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="44">
         <f>SUM(B24:H24)</f>
         <v/>
       </c>
@@ -7404,28 +7539,28 @@
           <t>Hand</t>
         </is>
       </c>
-      <c r="B25" s="42" t="n">
+      <c r="B25" s="43" t="n">
         <v>2394.35</v>
       </c>
-      <c r="C25" s="42" t="n">
+      <c r="C25" s="43" t="n">
         <v>2227.4</v>
       </c>
-      <c r="D25" s="42" t="n">
+      <c r="D25" s="43" t="n">
         <v>4971.03</v>
       </c>
-      <c r="E25" s="42" t="n">
+      <c r="E25" s="43" t="n">
         <v>6116.73</v>
       </c>
-      <c r="F25" s="42" t="n">
+      <c r="F25" s="43" t="n">
         <v>14117.7</v>
       </c>
-      <c r="G25" s="42" t="n">
+      <c r="G25" s="43" t="n">
         <v>18205.08</v>
       </c>
-      <c r="H25" s="42" t="n">
+      <c r="H25" s="43" t="n">
         <v>14970.97</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="44">
         <f>SUM(B25:H25)</f>
         <v/>
       </c>
@@ -7436,28 +7571,28 @@
           <t>Brand / other</t>
         </is>
       </c>
-      <c r="B26" s="42" t="n">
+      <c r="B26" s="43" t="n">
         <v>19000.09</v>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="43" t="n">
         <v>17646.93</v>
       </c>
-      <c r="D26" s="42" t="n">
+      <c r="D26" s="43" t="n">
         <v>32051.13</v>
       </c>
-      <c r="E26" s="42" t="n">
+      <c r="E26" s="43" t="n">
         <v>23388.84</v>
       </c>
-      <c r="F26" s="42" t="n">
+      <c r="F26" s="43" t="n">
         <v>17399</v>
       </c>
-      <c r="G26" s="42" t="n">
+      <c r="G26" s="43" t="n">
         <v>12322.14</v>
       </c>
-      <c r="H26" s="42" t="n">
+      <c r="H26" s="43" t="n">
         <v>11793.89</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="44">
         <f>SUM(B26:H26)</f>
         <v/>
       </c>
@@ -7468,35 +7603,35 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B27" s="52">
+      <c r="B27" s="53">
         <f>SUM(B22:B26)</f>
         <v/>
       </c>
-      <c r="C27" s="52">
+      <c r="C27" s="53">
         <f>SUM(C22:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="52">
+      <c r="D27" s="53">
         <f>SUM(D22:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="52">
+      <c r="E27" s="53">
         <f>SUM(E22:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="52">
+      <c r="F27" s="53">
         <f>SUM(F22:F26)</f>
         <v/>
       </c>
-      <c r="G27" s="52">
+      <c r="G27" s="53">
         <f>SUM(G22:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="52">
+      <c r="H27" s="53">
         <f>SUM(H22:H26)</f>
         <v/>
       </c>
-      <c r="I27" s="52">
+      <c r="I27" s="53">
         <f>SUM(I22:I26)</f>
         <v/>
       </c>
@@ -7835,25 +7970,25 @@
           <t>Ortho</t>
         </is>
       </c>
-      <c r="B44" s="44" t="n">
+      <c r="B44" s="45" t="n">
         <v>730.89</v>
       </c>
-      <c r="C44" s="44" t="n">
+      <c r="C44" s="45" t="n">
         <v>487.45</v>
       </c>
-      <c r="D44" s="44" t="n">
+      <c r="D44" s="45" t="n">
         <v>885.51</v>
       </c>
-      <c r="E44" s="44" t="n">
+      <c r="E44" s="45" t="n">
         <v>757.78</v>
       </c>
-      <c r="F44" s="44" t="n">
+      <c r="F44" s="45" t="n">
         <v>549.11</v>
       </c>
-      <c r="G44" s="44" t="n">
+      <c r="G44" s="45" t="n">
         <v>1091.87</v>
       </c>
-      <c r="H44" s="44" t="n">
+      <c r="H44" s="45" t="n">
         <v>1330.7</v>
       </c>
       <c r="I44" s="19">
@@ -7867,25 +8002,25 @@
           <t>Spine</t>
         </is>
       </c>
-      <c r="B45" s="44" t="n">
+      <c r="B45" s="45" t="n">
         <v>216.06</v>
       </c>
-      <c r="C45" s="44" t="n">
+      <c r="C45" s="45" t="n">
         <v>115.82</v>
       </c>
-      <c r="D45" s="44" t="n">
+      <c r="D45" s="45" t="n">
         <v>221.03</v>
       </c>
-      <c r="E45" s="44" t="n">
+      <c r="E45" s="45" t="n">
         <v>192.65</v>
       </c>
-      <c r="F45" s="44" t="n">
+      <c r="F45" s="45" t="n">
         <v>162.94</v>
       </c>
-      <c r="G45" s="44" t="n">
+      <c r="G45" s="45" t="n">
         <v>418.47</v>
       </c>
-      <c r="H45" s="44" t="n">
+      <c r="H45" s="45" t="n">
         <v>373.67</v>
       </c>
       <c r="I45" s="19">
@@ -7899,25 +8034,25 @@
           <t>Foot</t>
         </is>
       </c>
-      <c r="B46" s="44" t="n">
+      <c r="B46" s="45" t="n">
         <v>44.03</v>
       </c>
-      <c r="C46" s="44" t="n">
+      <c r="C46" s="45" t="n">
         <v>60.99</v>
       </c>
-      <c r="D46" s="44" t="n">
+      <c r="D46" s="45" t="n">
         <v>88.18000000000001</v>
       </c>
-      <c r="E46" s="44" t="n">
+      <c r="E46" s="45" t="n">
         <v>80.14</v>
       </c>
-      <c r="F46" s="44" t="n">
+      <c r="F46" s="45" t="n">
         <v>67.38</v>
       </c>
-      <c r="G46" s="44" t="n">
+      <c r="G46" s="45" t="n">
         <v>153.29</v>
       </c>
-      <c r="H46" s="44" t="n">
+      <c r="H46" s="45" t="n">
         <v>132.56</v>
       </c>
       <c r="I46" s="19">
@@ -7931,25 +8066,25 @@
           <t>Hand</t>
         </is>
       </c>
-      <c r="B47" s="44" t="n">
+      <c r="B47" s="45" t="n">
         <v>78.98</v>
       </c>
-      <c r="C47" s="44" t="n">
+      <c r="C47" s="45" t="n">
         <v>40</v>
       </c>
-      <c r="D47" s="44" t="n">
+      <c r="D47" s="45" t="n">
         <v>140.57</v>
       </c>
-      <c r="E47" s="44" t="n">
+      <c r="E47" s="45" t="n">
         <v>139.82</v>
       </c>
-      <c r="F47" s="44" t="n">
+      <c r="F47" s="45" t="n">
         <v>212.47</v>
       </c>
-      <c r="G47" s="44" t="n">
+      <c r="G47" s="45" t="n">
         <v>320.05</v>
       </c>
-      <c r="H47" s="44" t="n">
+      <c r="H47" s="45" t="n">
         <v>355.16</v>
       </c>
       <c r="I47" s="19">
@@ -7963,25 +8098,25 @@
           <t>Brand / other</t>
         </is>
       </c>
-      <c r="B48" s="44" t="n">
+      <c r="B48" s="45" t="n">
         <v>414.91</v>
       </c>
-      <c r="C48" s="44" t="n">
+      <c r="C48" s="45" t="n">
         <v>424.19</v>
       </c>
-      <c r="D48" s="44" t="n">
+      <c r="D48" s="45" t="n">
         <v>645.59</v>
       </c>
-      <c r="E48" s="44" t="n">
+      <c r="E48" s="45" t="n">
         <v>511.72</v>
       </c>
-      <c r="F48" s="44" t="n">
+      <c r="F48" s="45" t="n">
         <v>463</v>
       </c>
-      <c r="G48" s="44" t="n">
+      <c r="G48" s="45" t="n">
         <v>1255.42</v>
       </c>
-      <c r="H48" s="44" t="n">
+      <c r="H48" s="45" t="n">
         <v>1293.13</v>
       </c>
       <c r="I48" s="19">
@@ -8116,11 +8251,11 @@
           <t>Ortho</t>
         </is>
       </c>
-      <c r="B58" s="49">
+      <c r="B58" s="50">
         <f>B22</f>
         <v/>
       </c>
-      <c r="C58" s="49">
+      <c r="C58" s="50">
         <f>H22</f>
         <v/>
       </c>
@@ -8155,11 +8290,11 @@
           <t>Spine</t>
         </is>
       </c>
-      <c r="B59" s="49">
+      <c r="B59" s="50">
         <f>B23</f>
         <v/>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>H23</f>
         <v/>
       </c>
@@ -8194,11 +8329,11 @@
           <t>Foot</t>
         </is>
       </c>
-      <c r="B60" s="49">
+      <c r="B60" s="50">
         <f>B24</f>
         <v/>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>H24</f>
         <v/>
       </c>
@@ -8233,11 +8368,11 @@
           <t>Hand</t>
         </is>
       </c>
-      <c r="B61" s="49">
+      <c r="B61" s="50">
         <f>B25</f>
         <v/>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>H25</f>
         <v/>
       </c>
@@ -8386,28 +8521,28 @@
           <t>Budget</t>
         </is>
       </c>
-      <c r="B6" s="53" t="n">
+      <c r="B6" s="54" t="n">
         <v>165000</v>
       </c>
-      <c r="C6" s="53" t="n">
+      <c r="C6" s="54" t="n">
         <v>165000</v>
       </c>
-      <c r="D6" s="53" t="n">
+      <c r="D6" s="54" t="n">
         <v>185000</v>
       </c>
-      <c r="E6" s="53" t="n">
+      <c r="E6" s="54" t="n">
         <v>185000</v>
       </c>
-      <c r="F6" s="53" t="n">
+      <c r="F6" s="54" t="n">
         <v>185000</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="54" t="n">
         <v>200000</v>
       </c>
-      <c r="H6" s="53" t="n">
+      <c r="H6" s="54" t="n">
         <v>200000</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="44">
         <f>SUM(B6:H6)</f>
         <v/>
       </c>
@@ -8418,28 +8553,28 @@
           <t>Actual spend</t>
         </is>
       </c>
-      <c r="B7" s="53" t="n">
+      <c r="B7" s="54" t="n">
         <v>169087.2</v>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="54" t="n">
         <v>139994.19</v>
       </c>
-      <c r="D7" s="53" t="n">
+      <c r="D7" s="54" t="n">
         <v>283541.48</v>
       </c>
-      <c r="E7" s="53" t="n">
+      <c r="E7" s="54" t="n">
         <v>241541.3</v>
       </c>
-      <c r="F7" s="53" t="n">
+      <c r="F7" s="54" t="n">
         <v>212153.77</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="54" t="n">
         <v>279448.97</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="54" t="n">
         <v>262408.99</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="44">
         <f>SUM(B7:H7)</f>
         <v/>
       </c>
@@ -8450,35 +8585,35 @@
           <t>Variance (over / under)</t>
         </is>
       </c>
-      <c r="B8" s="54">
+      <c r="B8" s="55">
         <f>B7-B6</f>
         <v/>
       </c>
-      <c r="C8" s="54">
+      <c r="C8" s="55">
         <f>C7-C6</f>
         <v/>
       </c>
-      <c r="D8" s="54">
+      <c r="D8" s="55">
         <f>D7-D6</f>
         <v/>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="55">
         <f>E7-E6</f>
         <v/>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="55">
         <f>F7-F6</f>
         <v/>
       </c>
-      <c r="G8" s="54">
+      <c r="G8" s="55">
         <f>G7-G6</f>
         <v/>
       </c>
-      <c r="H8" s="54">
+      <c r="H8" s="55">
         <f>H7-H6</f>
         <v/>
       </c>
-      <c r="I8" s="54">
+      <c r="I8" s="55">
         <f>I7-I6</f>
         <v/>
       </c>
@@ -8581,14 +8716,14 @@
           <t>Paid Search - Google</t>
         </is>
       </c>
-      <c r="B16" s="53" t="n">
+      <c r="B16" s="54" t="n">
         <v>1285000</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="56">
         <f>I7</f>
         <v/>
       </c>
-      <c r="D16" s="56">
+      <c r="D16" s="57">
         <f>C16-B16</f>
         <v/>
       </c>
@@ -8596,7 +8731,7 @@
         <f>C16/B16-1</f>
         <v/>
       </c>
-      <c r="F16" s="36" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Verified from the Google Ads export.</t>
         </is>
@@ -8608,25 +8743,25 @@
           <t>All other OpEx lines</t>
         </is>
       </c>
-      <c r="B17" s="53" t="n">
+      <c r="B17" s="54" t="n">
         <v>720416.83</v>
       </c>
-      <c r="C17" s="57" t="inlineStr">
+      <c r="C17" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="57" t="inlineStr">
+      <c r="D17" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="57" t="inlineStr">
+      <c r="E17" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="36" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>NOT VERIFIED. No invoice or spend data supplied — budget shown as a placeholder.</t>
         </is>
@@ -8638,25 +8773,25 @@
           <t>CapEx plan</t>
         </is>
       </c>
-      <c r="B18" s="53" t="n">
+      <c r="B18" s="54" t="n">
         <v>158000</v>
       </c>
-      <c r="C18" s="57" t="inlineStr">
+      <c r="C18" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="57" t="inlineStr">
+      <c r="D18" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="57" t="inlineStr">
+      <c r="E18" s="58" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>NOT VERIFIED. No spend data supplied.</t>
         </is>
@@ -8668,14 +8803,14 @@
           <t>TOTAL Jan-Jul plan</t>
         </is>
       </c>
-      <c r="B19" s="52">
+      <c r="B19" s="53">
         <f>SUM(B16:B18)</f>
         <v/>
       </c>
-      <c r="C19" s="58" t="n"/>
-      <c r="D19" s="58" t="n"/>
-      <c r="E19" s="58" t="n"/>
-      <c r="F19" s="59" t="inlineStr">
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>Cannot be closed out until the other lines are supplied.</t>
         </is>
@@ -8730,16 +8865,16 @@
           <t>Paid-search cost per new patient</t>
         </is>
       </c>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>$105</t>
         </is>
       </c>
-      <c r="C26" s="61">
+      <c r="C26" s="62">
         <f>I7/Actuals!N12</f>
         <v/>
       </c>
-      <c r="D26" s="40" t="inlineStr">
+      <c r="D26" s="41" t="inlineStr">
         <is>
           <t>Actual divides ALL Google spend by ALL new patients from every source, so it flatters paid search and is still 2x the plan.</t>
         </is>
@@ -8751,16 +8886,16 @@
           <t>New patients (annual)</t>
         </is>
       </c>
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>14,400</t>
         </is>
       </c>
-      <c r="C27" s="62">
+      <c r="C27" s="63">
         <f>Trends!F36</f>
         <v/>
       </c>
-      <c r="D27" s="40" t="inlineStr">
+      <c r="D27" s="41" t="inlineStr">
         <is>
           <t>Full-year projection at the current run rate, from the Trends tab.</t>
         </is>
@@ -8772,17 +8907,17 @@
           <t>Blended revenue per new patient</t>
         </is>
       </c>
-      <c r="B28" s="60" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>$650</t>
         </is>
       </c>
-      <c r="C28" s="62" t="inlineStr">
+      <c r="C28" s="63" t="inlineStr">
         <is>
           <t>not verified</t>
         </is>
       </c>
-      <c r="D28" s="40" t="inlineStr">
+      <c r="D28" s="41" t="inlineStr">
         <is>
           <t>Finance owns this; no actual supplied.</t>
         </is>
@@ -8880,7 +9015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8938,10 +9073,10 @@
           <t>Annualisation factor</t>
         </is>
       </c>
-      <c r="B6" s="63" t="n">
+      <c r="B6" s="64" t="n">
         <v>2.967479674796748</v>
       </c>
-      <c r="C6" s="40" t="inlineStr">
+      <c r="C6" s="41" t="inlineStr">
         <is>
           <t>365 days / 123 days in the observed window.</t>
         </is>
@@ -8953,10 +9088,10 @@
           <t>Realised new patients per booked slot</t>
         </is>
       </c>
-      <c r="B7" s="64" t="n">
+      <c r="B7" s="65" t="n">
         <v>0.1246864922966679</v>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="41" t="inlineStr">
         <is>
           <t>EMR new patients 30 Mar-30 Jul (4,524) divided by booked core-line slots (36,283). Calibrated, not assumed.</t>
         </is>
@@ -8968,10 +9103,10 @@
           <t>Practical maximum utilisation</t>
         </is>
       </c>
-      <c r="B8" s="64" t="n">
+      <c r="B8" s="65" t="n">
         <v>0.9</v>
       </c>
-      <c r="C8" s="40" t="inlineStr">
+      <c r="C8" s="41" t="inlineStr">
         <is>
           <t>Allows for cancellations, no-shows and schedule buffer. 100% is not an operating target.</t>
         </is>
@@ -8980,230 +9115,110 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>The appointment file books 19.4% of visits as "New Patient", but only 12.5% of booked slots become a counted new patient in the EMR.</t>
+          <t>EVERY appointment type is one 5-minute slot — 95% of new patients and 99% of follow-ups. A new patient consumes exactly the same</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>That 36% gap is cancellations, no-shows, and records excluded by the EMR export filters. It is a real number to investigate, not an error here.</t>
+          <t>schedule unit as a follow-up, so one unused slot is one bookable appointment and could be a new patient just as easily.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>The appointment file books 19.4% of visits as "New Patient", of which 64.3% become a counted new patient in the EMR (12.5% of all</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>booked slots). The 35.7% shortfall is cancellations, no-shows, and records excluded by the EMR export filters — worth investigating.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANT: the 12.5% factor holds TODAYS appointment mix constant. It is the floor on what headroom is worth, not the ceiling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>See the mix-shift scenario below — what the empty slots are worth depends entirely on what you choose to book into them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Addressable market inside existing physician clinic time — by service line</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Service line</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Slots available</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Slots booked</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Utilisation</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Unused slots</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Annual new-patient capacity at 100%</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Annual new patients at 90% utilisation</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Annual new patients at current rate</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Headroom to 90%</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Spine</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>9889</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>6467</v>
-      </c>
-      <c r="D15" s="23">
-        <f>C15/B15</f>
-        <v/>
-      </c>
-      <c r="E15" s="32">
-        <f>B15-C15</f>
-        <v/>
-      </c>
-      <c r="F15" s="32">
-        <f>B15*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G15" s="32">
-        <f>B15*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H15" s="32">
-        <f>C15*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I15" s="21">
-        <f>G15-H15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Ortho</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>15400</v>
-      </c>
-      <c r="C16" s="7" t="n">
-        <v>12167</v>
-      </c>
-      <c r="D16" s="23">
-        <f>C16/B16</f>
-        <v/>
-      </c>
-      <c r="E16" s="32">
-        <f>B16-C16</f>
-        <v/>
-      </c>
-      <c r="F16" s="32">
-        <f>B16*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G16" s="32">
-        <f>B16*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H16" s="32">
-        <f>C16*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>G16-H16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Foot</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="n">
-        <v>8325</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>5873</v>
-      </c>
-      <c r="D17" s="23">
-        <f>C17/B17</f>
-        <v/>
-      </c>
-      <c r="E17" s="32">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>B17*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G17" s="32">
-        <f>B17*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H17" s="32">
-        <f>C17*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I17" s="21">
-        <f>G17-H17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Pain</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>10393</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>9348</v>
-      </c>
-      <c r="D18" s="23">
-        <f>C18/B18</f>
-        <v/>
-      </c>
-      <c r="E18" s="32">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-      <c r="F18" s="32">
-        <f>B18*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G18" s="32">
-        <f>B18*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H18" s="32">
-        <f>C18*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I18" s="21">
-        <f>G18-H18</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Hand</t>
+          <t>Spine</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>2419</v>
+        <v>9889</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>2428</v>
+        <v>6467</v>
       </c>
       <c r="D19" s="23">
         <f>C19/B19</f>
@@ -9231,271 +9246,271 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Ortho</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>15400</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>12167</v>
+      </c>
+      <c r="D20" s="23">
+        <f>C20/B20</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>B20*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G20" s="32">
+        <f>B20*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H20" s="32">
+        <f>C20*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I20" s="21">
+        <f>G20-H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Foot</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>8325</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>5873</v>
+      </c>
+      <c r="D21" s="23">
+        <f>C21/B21</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>B21*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G21" s="32">
+        <f>B21*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H21" s="32">
+        <f>C21*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I21" s="21">
+        <f>G21-H21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Pain</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>10393</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>9348</v>
+      </c>
+      <c r="D22" s="23">
+        <f>C22/B22</f>
+        <v/>
+      </c>
+      <c r="E22" s="32">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="F22" s="32">
+        <f>B22*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
+        <f>B22*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H22" s="32">
+        <f>C22*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I22" s="21">
+        <f>G22-H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Hand</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>2419</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>2428</v>
+      </c>
+      <c r="D23" s="23">
+        <f>C23/B23</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>B23*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G23" s="32">
+        <f>B23*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H23" s="32">
+        <f>C23*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I23" s="21">
+        <f>G23-H23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B20" s="11">
-        <f>SUM(B15:B19)</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>SUM(C15:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>C20/B20</f>
-        <v/>
-      </c>
-      <c r="E20" s="11">
-        <f>SUM(E15:E19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="11">
-        <f>SUM(F15:F19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="11">
-        <f>SUM(G15:G19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="11">
-        <f>SUM(H15:H19)</f>
-        <v/>
-      </c>
-      <c r="I20" s="22">
-        <f>G20-H20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="B24" s="11">
+        <f>SUM(B19:B23)</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>SUM(C19:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>C24/B24</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>SUM(E19:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>SUM(F19:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>SUM(G19:G23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="11">
+        <f>SUM(H19:H23)</f>
+        <v/>
+      </c>
+      <c r="I24" s="22">
+        <f>G24-H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Read the headroom column as: additional new patients per year available from clinic time these physicians ALREADY have on the schedule.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>It requires no new hires, no new sites and no additional marketing reach — only filling sessions that are already being offered.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Addressable market by hub</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Hub</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Slots available</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Slots booked</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Utilisation</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Unused slots</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>Annual new-patient capacity at 100%</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Annual new patients at 90% utilisation</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Annual new patients at current rate</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>Headroom to 90%</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Sterling Heights</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>16531</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>12506</v>
-      </c>
-      <c r="D27" s="23">
-        <f>C27/B27</f>
-        <v/>
-      </c>
-      <c r="E27" s="32">
-        <f>B27-C27</f>
-        <v/>
-      </c>
-      <c r="F27" s="32">
-        <f>B27*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G27" s="32">
-        <f>B27*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H27" s="32">
-        <f>C27*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I27" s="21">
-        <f>G27-H27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Southfield</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="n">
-        <v>6794</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>4574</v>
-      </c>
-      <c r="D28" s="23">
-        <f>C28/B28</f>
-        <v/>
-      </c>
-      <c r="E28" s="32">
-        <f>B28-C28</f>
-        <v/>
-      </c>
-      <c r="F28" s="32">
-        <f>B28*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G28" s="32">
-        <f>B28*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H28" s="32">
-        <f>C28*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I28" s="21">
-        <f>G28-H28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Livonia</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>20512</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>17354</v>
-      </c>
-      <c r="D29" s="23">
-        <f>C29/B29</f>
-        <v/>
-      </c>
-      <c r="E29" s="32">
-        <f>B29-C29</f>
-        <v/>
-      </c>
-      <c r="F29" s="32">
-        <f>B29*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G29" s="32">
-        <f>B29*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H29" s="32">
-        <f>C29*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I29" s="21">
-        <f>G29-H29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Port Huron</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>1609</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>1199</v>
-      </c>
-      <c r="D30" s="23">
-        <f>C30/B30</f>
-        <v/>
-      </c>
-      <c r="E30" s="32">
-        <f>B30-C30</f>
-        <v/>
-      </c>
-      <c r="F30" s="32">
-        <f>B30*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="G30" s="32">
-        <f>B30*$B$6*$B$8*$B$7</f>
-        <v/>
-      </c>
-      <c r="H30" s="32">
-        <f>C30*$B$6*$B$7</f>
-        <v/>
-      </c>
-      <c r="I30" s="21">
-        <f>G30-H30</f>
-        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Sterling Heights</t>
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>980</v>
+        <v>16531</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>650</v>
+        <v>12506</v>
       </c>
       <c r="D31" s="23">
         <f>C31/B31</f>
@@ -9523,513 +9538,763 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Southfield</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>6794</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>4574</v>
+      </c>
+      <c r="D32" s="23">
+        <f>C32/B32</f>
+        <v/>
+      </c>
+      <c r="E32" s="32">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="F32" s="32">
+        <f>B32*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G32" s="32">
+        <f>B32*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H32" s="32">
+        <f>C32*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I32" s="21">
+        <f>G32-H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Livonia</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n">
+        <v>20512</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>17354</v>
+      </c>
+      <c r="D33" s="23">
+        <f>C33/B33</f>
+        <v/>
+      </c>
+      <c r="E33" s="32">
+        <f>B33-C33</f>
+        <v/>
+      </c>
+      <c r="F33" s="32">
+        <f>B33*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G33" s="32">
+        <f>B33*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H33" s="32">
+        <f>C33*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I33" s="21">
+        <f>G33-H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Port Huron</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>1609</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D34" s="23">
+        <f>C34/B34</f>
+        <v/>
+      </c>
+      <c r="E34" s="32">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="F34" s="32">
+        <f>B34*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G34" s="32">
+        <f>B34*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H34" s="32">
+        <f>C34*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I34" s="21">
+        <f>G34-H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Troy</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>980</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="D35" s="23">
+        <f>C35/B35</f>
+        <v/>
+      </c>
+      <c r="E35" s="32">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="F35" s="32">
+        <f>B35*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="G35" s="32">
+        <f>B35*$B$6*$B$8*$B$7</f>
+        <v/>
+      </c>
+      <c r="H35" s="32">
+        <f>C35*$B$6*$B$7</f>
+        <v/>
+      </c>
+      <c r="I35" s="21">
+        <f>G35-H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B32" s="11">
-        <f>SUM(B27:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="11">
-        <f>SUM(C27:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="24">
-        <f>C32/B32</f>
-        <v/>
-      </c>
-      <c r="E32" s="11">
-        <f>SUM(E27:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="11">
-        <f>SUM(F27:F31)</f>
-        <v/>
-      </c>
-      <c r="G32" s="11">
-        <f>SUM(G27:G31)</f>
-        <v/>
-      </c>
-      <c r="H32" s="11">
-        <f>SUM(H27:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="22">
-        <f>G32-H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="B36" s="11">
+        <f>SUM(B31:B35)</f>
+        <v/>
+      </c>
+      <c r="C36" s="11">
+        <f>SUM(C31:C35)</f>
+        <v/>
+      </c>
+      <c r="D36" s="24">
+        <f>C36/B36</f>
+        <v/>
+      </c>
+      <c r="E36" s="11">
+        <f>SUM(E31:E35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="11">
+        <f>SUM(F31:F35)</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>SUM(G31:G35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="11">
+        <f>SUM(H31:H35)</f>
+        <v/>
+      </c>
+      <c r="I36" s="22">
+        <f>G36-H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Livonia is effectively full at 85%. Sterling Heights and Southfield hold nearly three quarters of the total headroom between them.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Why Friday is light — capacity offered, not demand</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Clinic days observed</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Provider-sessions per day</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Slots offered per day</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Slots booked per day</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Utilisation</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Unused slots per day</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C38" s="28" t="n">
-        <v>18.55555555555556</v>
-      </c>
-      <c r="D38" s="32" t="n">
-        <v>581.4444444444445</v>
-      </c>
-      <c r="E38" s="32" t="n">
-        <v>432.3333333333333</v>
-      </c>
-      <c r="F38" s="23" t="n">
-        <v>0.7435505446206765</v>
-      </c>
-      <c r="G38" s="32" t="n">
-        <v>149.1111111111111</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C39" s="28" t="n">
-        <v>17.77777777777778</v>
-      </c>
-      <c r="D39" s="32" t="n">
-        <v>601.5</v>
-      </c>
-      <c r="E39" s="32" t="n">
-        <v>510.2222222222222</v>
-      </c>
-      <c r="F39" s="23" t="n">
-        <v>0.848249746005357</v>
-      </c>
-      <c r="G39" s="32" t="n">
-        <v>91.27777777777777</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C40" s="28" t="n">
-        <v>22.05555555555556</v>
-      </c>
-      <c r="D40" s="32" t="n">
-        <v>558.5</v>
-      </c>
-      <c r="E40" s="32" t="n">
-        <v>428.3888888888889</v>
-      </c>
-      <c r="F40" s="23" t="n">
-        <v>0.7670347160051726</v>
-      </c>
-      <c r="G40" s="32" t="n">
-        <v>130.1111111111111</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="C41" s="28" t="n">
-        <v>19.22222222222222</v>
-      </c>
-      <c r="D41" s="32" t="n">
-        <v>551.1666666666666</v>
-      </c>
-      <c r="E41" s="32" t="n">
-        <v>423.7222222222222</v>
-      </c>
-      <c r="F41" s="23" t="n">
-        <v>0.7687733091422235</v>
-      </c>
-      <c r="G41" s="32" t="n">
-        <v>127.4444444444444</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>18.55555555555556</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>581.4444444444445</v>
+      </c>
+      <c r="E42" s="32" t="n">
+        <v>432.3333333333333</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>0.7435505446206765</v>
+      </c>
+      <c r="G42" s="32" t="n">
+        <v>149.1111111111111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C43" s="28" t="n">
+        <v>17.77777777777778</v>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>601.5</v>
+      </c>
+      <c r="E43" s="32" t="n">
+        <v>510.2222222222222</v>
+      </c>
+      <c r="F43" s="23" t="n">
+        <v>0.848249746005357</v>
+      </c>
+      <c r="G43" s="32" t="n">
+        <v>91.27777777777777</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" s="28" t="n">
+        <v>22.05555555555556</v>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>558.5</v>
+      </c>
+      <c r="E44" s="32" t="n">
+        <v>428.3888888888889</v>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>0.7670347160051726</v>
+      </c>
+      <c r="G44" s="32" t="n">
+        <v>130.1111111111111</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C45" s="28" t="n">
+        <v>19.22222222222222</v>
+      </c>
+      <c r="D45" s="32" t="n">
+        <v>551.1666666666666</v>
+      </c>
+      <c r="E45" s="32" t="n">
+        <v>423.7222222222222</v>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>0.7687733091422235</v>
+      </c>
+      <c r="G45" s="32" t="n">
+        <v>127.4444444444444</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n">
+      <c r="B46" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="C42" s="28" t="n">
+      <c r="C46" s="28" t="n">
         <v>12.11764705882353</v>
       </c>
-      <c r="D42" s="32" t="n">
+      <c r="D46" s="32" t="n">
         <v>303.4705882352941</v>
       </c>
-      <c r="E42" s="32" t="n">
+      <c r="E46" s="32" t="n">
         <v>234.0588235294118</v>
       </c>
-      <c r="F42" s="23" t="n">
+      <c r="F46" s="23" t="n">
         <v>0.7712735026167862</v>
       </c>
-      <c r="G42" s="32" t="n">
+      <c r="G46" s="32" t="n">
         <v>69.41176470588235</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Friday utilisation (77%) matches Wednesday and Thursday and beats Monday. Friday clinics fill perfectly well.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Friday simply offers 45% fewer slots and runs a third fewer provider-sessions. The light Friday is a scheduling decision, not weak demand.</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Scenario — staffing Friday like Thursday</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>Extra slots per Friday</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>247.6960784313725</v>
-      </c>
-      <c r="C49" s="36" t="inlineStr">
-        <is>
-          <t>Thursday slots per day less Friday slots per day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Friday fill rate applied</t>
-        </is>
-      </c>
-      <c r="B50" s="64" t="n">
-        <v>0.7712735026167862</v>
-      </c>
-      <c r="C50" s="36" t="inlineStr">
-        <is>
-          <t>Fridays already fill at this rate, so new Friday slots are assumed to fill the same way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>Extra new patients per Friday</t>
-        </is>
-      </c>
-      <c r="B51" s="19">
-        <f>B49*B50*$B$7</f>
-        <v/>
-      </c>
-      <c r="C51" s="36" t="inlineStr">
-        <is>
-          <t>Extra slots x fill rate x realised new patients per booked slot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>Fridays per year</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="C52" s="36" t="inlineStr">
-        <is>
-          <t>Allows for holidays.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
+          <t>Extra slots per Friday</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>247.6960784313725</v>
+      </c>
+      <c r="C53" s="37" t="inlineStr">
+        <is>
+          <t>Thursday slots per day less Friday slots per day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Friday fill rate applied</t>
+        </is>
+      </c>
+      <c r="B54" s="65" t="n">
+        <v>0.7712735026167862</v>
+      </c>
+      <c r="C54" s="37" t="inlineStr">
+        <is>
+          <t>Fridays already fill at this rate, so new Friday slots are assumed to fill the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Extra new patients per Friday</t>
+        </is>
+      </c>
+      <c r="B55" s="19">
+        <f>B53*B54*$B$7</f>
+        <v/>
+      </c>
+      <c r="C55" s="37" t="inlineStr">
+        <is>
+          <t>Extra slots x fill rate x realised new patients per booked slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Fridays per year</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C56" s="37" t="inlineStr">
+        <is>
+          <t>Allows for holidays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
           <t>Extra new patients per year</t>
         </is>
       </c>
-      <c r="B53" s="9">
-        <f>B51*B52</f>
-        <v/>
-      </c>
-      <c r="C53" s="36" t="inlineStr">
+      <c r="B57" s="9">
+        <f>B55*B56</f>
+        <v/>
+      </c>
+      <c r="C57" s="37" t="inlineStr">
         <is>
           <t>The prize for putting more physician time into Fridays.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>What the whole picture adds up to</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="44" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Ceiling</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>What the empty slots are worth depends on what you book into them</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Slots per year</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>New patients per year</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>What it assumes</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="26" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>2026 budget</t>
-        </is>
-      </c>
-      <c r="B57" s="9">
-        <f>Budget!N12</f>
-        <v/>
-      </c>
-      <c r="C57" s="40" t="inlineStr">
-        <is>
-          <t>The plan as written.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="26" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Current run rate</t>
-        </is>
-      </c>
-      <c r="B58" s="9">
-        <f>H20</f>
-        <v/>
-      </c>
-      <c r="C58" s="40" t="inlineStr">
-        <is>
-          <t>Core service lines at the 30 Mar - 30 Jul booking rate, annualised.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="26" customHeight="1">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>Fill existing schedule to 90%</t>
-        </is>
-      </c>
-      <c r="B59" s="9">
-        <f>G20</f>
-        <v/>
-      </c>
-      <c r="C59" s="40" t="inlineStr">
-        <is>
-          <t>No new physicians, no new sites, no extra marketing reach. Fill sessions already offered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="26" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Plus Friday staffed like Thursday</t>
-        </is>
-      </c>
-      <c r="B60" s="9">
-        <f>G20+B53</f>
-        <v/>
-      </c>
-      <c r="C60" s="40" t="inlineStr">
-        <is>
-          <t>Adds physician time on Fridays at the fill rate Fridays already achieve.</t>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Absolute ceiling of current schedule</t>
-        </is>
-      </c>
-      <c r="B61" s="9">
-        <f>F20</f>
-        <v/>
-      </c>
-      <c r="C61" s="40" t="inlineStr">
-        <is>
-          <t>100% utilisation. Not an operating target — shown as the hard boundary.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>The headline: the 2026 budget sits BELOW the ceiling of the clinic time these physicians are already offering. The plan is reachable</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>without hiring, provided utilisation moves from 78% to 90% — and Spine, Southfield and Sterling Heights are where that slack sits.</t>
+          <t>Headroom to 90% utilisation</t>
+        </is>
+      </c>
+      <c r="B61" s="32">
+        <f>(B24*$B$8-C24)*$B$6</f>
+        <v/>
+      </c>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="41" t="inlineStr">
+        <is>
+          <t>Slots freed by moving from 78% to 90% utilisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>a) filled at todays appointment mix</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n"/>
+      <c r="C62" s="9">
+        <f>B61*$B$7</f>
+        <v/>
+      </c>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>Business as usual: the same blend of follow-ups and new patients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>b) filled entirely with new patients</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n"/>
+      <c r="C63" s="9">
+        <f>B61*$B$7/0.194</f>
+        <v/>
+      </c>
+      <c r="D63" s="41" t="inlineStr">
+        <is>
+          <t>Every freed slot deliberately booked as a new patient, at the 64.3% realisation rate.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>The true value of the headroom sits between these two lines. Capacity is not the binding constraint on the 2026 plan —</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>the constraint is how much of the open schedule gets deliberately allocated to new patients rather than follow-ups.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>What the whole picture adds up to</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Ceiling</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>New patients per year</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>What it assumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>2026 budget</t>
+        </is>
+      </c>
+      <c r="B70" s="9">
+        <f>Budget!N12</f>
+        <v/>
+      </c>
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>The plan as written.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Current run rate</t>
+        </is>
+      </c>
+      <c r="B71" s="9">
+        <f>H24</f>
+        <v/>
+      </c>
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>Core service lines at the 30 Mar - 30 Jul booking rate, annualised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Fill existing schedule to 90%</t>
+        </is>
+      </c>
+      <c r="B72" s="9">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>No new physicians, no new sites, no extra marketing reach. Fill sessions already offered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Plus Friday staffed like Thursday</t>
+        </is>
+      </c>
+      <c r="B73" s="9">
+        <f>G24+B57</f>
+        <v/>
+      </c>
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>Adds physician time on Fridays at the fill rate Fridays already achieve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Absolute ceiling of current schedule</t>
+        </is>
+      </c>
+      <c r="B74" s="9">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>100% utilisation. Not an operating target — shown as the hard boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>The headline: the 2026 budget sits WELL BELOW the ceiling of the clinic time these physicians already offer. Reaching it needs about</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>22% of the open Aug-Dec slots booked as new patients — roughly 2,840 of ~12,600. Capacity is not what is stopping the plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Spine, Sterling Heights and Southfield hold most of the slack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
           <t>Caveat: this measures appointment slots, not operating-room time, imaging, staffing ratios or payer mix. Ops owns those constraints.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Limits of this analysis</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Window is 30 March to 30 July 2026 only. Earlier months are not in the capacity file, so seasonality is not captured.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Slot counts come from the published schedule. A slot that exists in the template but that a provider never intended to work still counts as available.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Service line is taken from the file’s own Lookup tab. PENS, X-ray, MA, PA and PCP are excluded as non-core at your direction.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Booked-to-realised conversion is a single blended factor. It almost certainly varies by line and hub; splitting it would sharpen every number here.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>This is a supply-side market size. It says what the current schedule can hold, not what the surrounding population demands.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A55:I55"/>
+  <mergeCells count="8">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A40:I40"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D15:D20">
+  <conditionalFormatting sqref="D19:D24">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
       <formula>0.75</formula>
     </cfRule>
@@ -10037,7 +10302,7 @@
       <formula>0.9</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D27:D32">
+  <conditionalFormatting sqref="D31:D36">
     <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="4">
       <formula>0.75</formula>
     </cfRule>
